--- a/template_FtoF_単体テスト仕様書兼成績書.xlsx
+++ b/template_FtoF_単体テスト仕様書兼成績書.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="197">
   <si>
     <t>試験日</t>
     <rPh sb="0" eb="3">
@@ -1629,19 +1629,6 @@
     <phoneticPr fontId="16"/>
   </si>
   <si>
-    <t>出力ファイルが可変長でないため検証不可</t>
-    <rPh sb="0" eb="2">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>カヘンチョウ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ケンショウフカ</t>
-    </rPh>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
     <t>前0埋めされていること。</t>
     <rPh sb="0" eb="1">
       <t>マエ</t>
@@ -1655,25 +1642,6 @@
     <t>固定長ファイル</t>
     <rPh sb="0" eb="3">
       <t>コテイチョウ</t>
-    </rPh>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>入力項目にマイナス値あり項目がないため検証不可</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>ケンショウフカ</t>
     </rPh>
     <phoneticPr fontId="16"/>
   </si>
@@ -1714,19 +1682,6 @@
     <phoneticPr fontId="16"/>
   </si>
   <si>
-    <t>コード変換処理がないため検証不可</t>
-    <rPh sb="3" eb="5">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>ケンショウフカ</t>
-    </rPh>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
     <t>本インターフェースでは、トリガーファイル出力が必要なためファイル出力先パスに、以下の2つのファイルが作成されていることを確認する。
 　・マッピング後ファイル
 　・トリガーファイル
@@ -1787,19 +1742,6 @@
   </si>
   <si>
     <t>指定桁数(固定長)未満パターン</t>
-  </si>
-  <si>
-    <t>全角項目以外の箇所の全角文字はシフトインアウトを含む。数値項目はテスト対象外（0埋めするため）</t>
-    <rPh sb="27" eb="31">
-      <t>スウチコウモク</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>タイショウガイ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>ISI</t>
@@ -1918,6 +1860,20 @@
   </si>
   <si>
     <t>tsvファイル。タブ区切りであること。</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>正常</t>
+    <rPh sb="0" eb="2">
+      <t>セイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>異常</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
     <phoneticPr fontId="16"/>
   </si>
 </sst>
@@ -2606,7 +2562,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2835,8 +2791,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="562">
+  <borders count="563">
     <border>
       <left/>
       <right/>
@@ -10377,6 +10339,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -19470,7 +19443,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="396">
+  <cellXfs count="404">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -19745,9 +19718,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="15" fillId="36" borderId="42" xfId="198" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19826,9 +19796,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="31" xfId="198" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -19858,9 +19825,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="198" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -19930,9 +19894,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="36" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -20026,9 +19987,6 @@
     <xf numFmtId="0" fontId="94" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="198" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="85" fillId="3" borderId="17" xfId="151" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -20099,9 +20057,6 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -20129,9 +20084,6 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="35" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -20222,30 +20174,15 @@
     <xf numFmtId="49" fontId="15" fillId="36" borderId="493" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="500" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="38" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="94" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -20261,9 +20198,6 @@
     <xf numFmtId="49" fontId="15" fillId="35" borderId="493" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="503" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="36" borderId="504" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -20318,9 +20252,6 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="511" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -20375,6 +20306,258 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="36" borderId="555" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="36" borderId="556" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="36" borderId="557" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="558" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="559" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="555" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="560" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="35" borderId="554" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="35" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="554" xfId="3258" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="555" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="45" xfId="3258" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="81" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="561" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="36" borderId="556" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="561" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="35" borderId="556" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="81" fillId="36" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="81" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="546" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="546" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="554" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="560" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="562" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="546" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="562" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="560" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="554" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="81" fillId="36" borderId="546" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="500" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="48" xfId="152" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="89" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -20399,33 +20582,6 @@
     <xf numFmtId="185" fontId="89" fillId="3" borderId="21" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="48" xfId="152" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="198" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -20486,179 +20642,20 @@
     <xf numFmtId="49" fontId="15" fillId="4" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="36" borderId="555" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="36" borderId="556" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="36" borderId="557" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="38" borderId="554" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="39" borderId="503" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="39" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="39" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="558" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="559" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="555" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="560" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="35" borderId="554" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="35" borderId="554" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="554" xfId="3258" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="555" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="45" xfId="3258" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="81" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="561" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="36" borderId="556" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="561" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="35" borderId="556" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="81" fillId="36" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="556" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="81" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="15" fillId="39" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3300">
@@ -24004,86 +24001,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>2743947</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>368674</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="吹き出し: 四角形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7E00E83-97C1-4368-9176-1A0CD2821735}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13525500" y="9315450"/>
-          <a:ext cx="3134472" cy="787774"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -70679"/>
-            <a:gd name="adj2" fmla="val 66968"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>コード変換処理がある場合に実施</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>（変換無しの場合グレーアウトして備考に変換項目なしと記載）</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -24377,1176 +24294,1176 @@
   <dimension ref="A1:BF32"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="14.45" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="3.5" style="189"/>
+    <col min="1" max="16384" width="3.5" style="184"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:58" ht="14.45" customHeight="1" thickTop="1">
-      <c r="A1" s="186"/>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
-      <c r="K1" s="187"/>
-      <c r="L1" s="187"/>
-      <c r="M1" s="187"/>
-      <c r="N1" s="187"/>
-      <c r="O1" s="187"/>
-      <c r="P1" s="187"/>
-      <c r="Q1" s="187"/>
-      <c r="R1" s="187"/>
-      <c r="S1" s="187"/>
-      <c r="T1" s="187"/>
-      <c r="U1" s="187"/>
-      <c r="V1" s="187"/>
-      <c r="W1" s="187"/>
-      <c r="X1" s="187"/>
-      <c r="Y1" s="187"/>
-      <c r="Z1" s="187"/>
-      <c r="AA1" s="187"/>
-      <c r="AB1" s="187"/>
-      <c r="AC1" s="187"/>
-      <c r="AD1" s="187"/>
-      <c r="AE1" s="187"/>
-      <c r="AF1" s="187"/>
-      <c r="AG1" s="187"/>
-      <c r="AH1" s="187"/>
-      <c r="AI1" s="187"/>
-      <c r="AJ1" s="187"/>
-      <c r="AK1" s="187"/>
-      <c r="AL1" s="187"/>
-      <c r="AM1" s="187"/>
-      <c r="AN1" s="187"/>
-      <c r="AO1" s="187"/>
-      <c r="AP1" s="187"/>
-      <c r="AQ1" s="187"/>
-      <c r="AR1" s="187"/>
-      <c r="AS1" s="187"/>
-      <c r="AT1" s="187"/>
-      <c r="AU1" s="187"/>
-      <c r="AV1" s="187"/>
-      <c r="AW1" s="187"/>
-      <c r="AX1" s="187"/>
-      <c r="AY1" s="188"/>
+      <c r="A1" s="181"/>
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="182"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="182"/>
+      <c r="U1" s="182"/>
+      <c r="V1" s="182"/>
+      <c r="W1" s="182"/>
+      <c r="X1" s="182"/>
+      <c r="Y1" s="182"/>
+      <c r="Z1" s="182"/>
+      <c r="AA1" s="182"/>
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="182"/>
+      <c r="AD1" s="182"/>
+      <c r="AE1" s="182"/>
+      <c r="AF1" s="182"/>
+      <c r="AG1" s="182"/>
+      <c r="AH1" s="182"/>
+      <c r="AI1" s="182"/>
+      <c r="AJ1" s="182"/>
+      <c r="AK1" s="182"/>
+      <c r="AL1" s="182"/>
+      <c r="AM1" s="182"/>
+      <c r="AN1" s="182"/>
+      <c r="AO1" s="182"/>
+      <c r="AP1" s="182"/>
+      <c r="AQ1" s="182"/>
+      <c r="AR1" s="182"/>
+      <c r="AS1" s="182"/>
+      <c r="AT1" s="182"/>
+      <c r="AU1" s="182"/>
+      <c r="AV1" s="182"/>
+      <c r="AW1" s="182"/>
+      <c r="AX1" s="182"/>
+      <c r="AY1" s="183"/>
     </row>
     <row r="2" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A2" s="190"/>
-      <c r="AY2" s="191"/>
+      <c r="A2" s="185"/>
+      <c r="AY2" s="186"/>
     </row>
     <row r="3" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A3" s="190"/>
-      <c r="C3" s="309" t="s">
+      <c r="A3" s="185"/>
+      <c r="C3" s="362" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="309"/>
-      <c r="E3" s="309"/>
-      <c r="F3" s="309"/>
-      <c r="G3" s="309"/>
-      <c r="H3" s="309"/>
-      <c r="I3" s="309"/>
-      <c r="J3" s="309"/>
-      <c r="K3" s="309"/>
-      <c r="L3" s="309"/>
-      <c r="M3" s="309"/>
-      <c r="N3" s="309"/>
-      <c r="O3" s="309"/>
-      <c r="P3" s="309"/>
-      <c r="Q3" s="309"/>
-      <c r="R3" s="309"/>
-      <c r="S3" s="309"/>
-      <c r="T3" s="309"/>
-      <c r="U3" s="309"/>
-      <c r="V3" s="309"/>
-      <c r="W3" s="309"/>
-      <c r="X3" s="309"/>
-      <c r="Y3" s="309"/>
-      <c r="Z3" s="309"/>
-      <c r="AA3" s="309"/>
-      <c r="AB3" s="309"/>
-      <c r="AC3" s="309"/>
-      <c r="AD3" s="309"/>
-      <c r="AE3" s="309"/>
-      <c r="AF3" s="309"/>
-      <c r="AG3" s="309"/>
-      <c r="AH3" s="309"/>
-      <c r="AI3" s="309"/>
-      <c r="AJ3" s="309"/>
-      <c r="AK3" s="309"/>
-      <c r="AL3" s="309"/>
-      <c r="AM3" s="309"/>
-      <c r="AN3" s="309"/>
-      <c r="AO3" s="309"/>
-      <c r="AP3" s="309"/>
-      <c r="AQ3" s="309"/>
-      <c r="AR3" s="309"/>
-      <c r="AS3" s="309"/>
-      <c r="AT3" s="309"/>
-      <c r="AU3" s="309"/>
-      <c r="AV3" s="309"/>
-      <c r="AW3" s="309"/>
-      <c r="AX3" s="309"/>
-      <c r="AY3" s="310"/>
+      <c r="D3" s="362"/>
+      <c r="E3" s="362"/>
+      <c r="F3" s="362"/>
+      <c r="G3" s="362"/>
+      <c r="H3" s="362"/>
+      <c r="I3" s="362"/>
+      <c r="J3" s="362"/>
+      <c r="K3" s="362"/>
+      <c r="L3" s="362"/>
+      <c r="M3" s="362"/>
+      <c r="N3" s="362"/>
+      <c r="O3" s="362"/>
+      <c r="P3" s="362"/>
+      <c r="Q3" s="362"/>
+      <c r="R3" s="362"/>
+      <c r="S3" s="362"/>
+      <c r="T3" s="362"/>
+      <c r="U3" s="362"/>
+      <c r="V3" s="362"/>
+      <c r="W3" s="362"/>
+      <c r="X3" s="362"/>
+      <c r="Y3" s="362"/>
+      <c r="Z3" s="362"/>
+      <c r="AA3" s="362"/>
+      <c r="AB3" s="362"/>
+      <c r="AC3" s="362"/>
+      <c r="AD3" s="362"/>
+      <c r="AE3" s="362"/>
+      <c r="AF3" s="362"/>
+      <c r="AG3" s="362"/>
+      <c r="AH3" s="362"/>
+      <c r="AI3" s="362"/>
+      <c r="AJ3" s="362"/>
+      <c r="AK3" s="362"/>
+      <c r="AL3" s="362"/>
+      <c r="AM3" s="362"/>
+      <c r="AN3" s="362"/>
+      <c r="AO3" s="362"/>
+      <c r="AP3" s="362"/>
+      <c r="AQ3" s="362"/>
+      <c r="AR3" s="362"/>
+      <c r="AS3" s="362"/>
+      <c r="AT3" s="362"/>
+      <c r="AU3" s="362"/>
+      <c r="AV3" s="362"/>
+      <c r="AW3" s="362"/>
+      <c r="AX3" s="362"/>
+      <c r="AY3" s="363"/>
     </row>
     <row r="4" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A4" s="190"/>
-      <c r="C4" s="309"/>
-      <c r="D4" s="309"/>
-      <c r="E4" s="309"/>
-      <c r="F4" s="309"/>
-      <c r="G4" s="309"/>
-      <c r="H4" s="309"/>
-      <c r="I4" s="309"/>
-      <c r="J4" s="309"/>
-      <c r="K4" s="309"/>
-      <c r="L4" s="309"/>
-      <c r="M4" s="309"/>
-      <c r="N4" s="309"/>
-      <c r="O4" s="309"/>
-      <c r="P4" s="309"/>
-      <c r="Q4" s="309"/>
-      <c r="R4" s="309"/>
-      <c r="S4" s="309"/>
-      <c r="T4" s="309"/>
-      <c r="U4" s="309"/>
-      <c r="V4" s="309"/>
-      <c r="W4" s="309"/>
-      <c r="X4" s="309"/>
-      <c r="Y4" s="309"/>
-      <c r="Z4" s="309"/>
-      <c r="AA4" s="309"/>
-      <c r="AB4" s="309"/>
-      <c r="AC4" s="309"/>
-      <c r="AD4" s="309"/>
-      <c r="AE4" s="309"/>
-      <c r="AF4" s="309"/>
-      <c r="AG4" s="309"/>
-      <c r="AH4" s="309"/>
-      <c r="AI4" s="309"/>
-      <c r="AJ4" s="309"/>
-      <c r="AK4" s="309"/>
-      <c r="AL4" s="309"/>
-      <c r="AM4" s="309"/>
-      <c r="AN4" s="309"/>
-      <c r="AO4" s="309"/>
-      <c r="AP4" s="309"/>
-      <c r="AQ4" s="309"/>
-      <c r="AR4" s="309"/>
-      <c r="AS4" s="309"/>
-      <c r="AT4" s="309"/>
-      <c r="AU4" s="309"/>
-      <c r="AV4" s="309"/>
-      <c r="AW4" s="309"/>
-      <c r="AX4" s="309"/>
-      <c r="AY4" s="310"/>
+      <c r="A4" s="185"/>
+      <c r="C4" s="362"/>
+      <c r="D4" s="362"/>
+      <c r="E4" s="362"/>
+      <c r="F4" s="362"/>
+      <c r="G4" s="362"/>
+      <c r="H4" s="362"/>
+      <c r="I4" s="362"/>
+      <c r="J4" s="362"/>
+      <c r="K4" s="362"/>
+      <c r="L4" s="362"/>
+      <c r="M4" s="362"/>
+      <c r="N4" s="362"/>
+      <c r="O4" s="362"/>
+      <c r="P4" s="362"/>
+      <c r="Q4" s="362"/>
+      <c r="R4" s="362"/>
+      <c r="S4" s="362"/>
+      <c r="T4" s="362"/>
+      <c r="U4" s="362"/>
+      <c r="V4" s="362"/>
+      <c r="W4" s="362"/>
+      <c r="X4" s="362"/>
+      <c r="Y4" s="362"/>
+      <c r="Z4" s="362"/>
+      <c r="AA4" s="362"/>
+      <c r="AB4" s="362"/>
+      <c r="AC4" s="362"/>
+      <c r="AD4" s="362"/>
+      <c r="AE4" s="362"/>
+      <c r="AF4" s="362"/>
+      <c r="AG4" s="362"/>
+      <c r="AH4" s="362"/>
+      <c r="AI4" s="362"/>
+      <c r="AJ4" s="362"/>
+      <c r="AK4" s="362"/>
+      <c r="AL4" s="362"/>
+      <c r="AM4" s="362"/>
+      <c r="AN4" s="362"/>
+      <c r="AO4" s="362"/>
+      <c r="AP4" s="362"/>
+      <c r="AQ4" s="362"/>
+      <c r="AR4" s="362"/>
+      <c r="AS4" s="362"/>
+      <c r="AT4" s="362"/>
+      <c r="AU4" s="362"/>
+      <c r="AV4" s="362"/>
+      <c r="AW4" s="362"/>
+      <c r="AX4" s="362"/>
+      <c r="AY4" s="363"/>
     </row>
     <row r="5" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A5" s="190"/>
-      <c r="AY5" s="191"/>
+      <c r="A5" s="185"/>
+      <c r="AY5" s="186"/>
     </row>
     <row r="6" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A6" s="311" t="s">
+      <c r="A6" s="364" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="312"/>
-      <c r="C6" s="312"/>
-      <c r="D6" s="312"/>
-      <c r="E6" s="312"/>
-      <c r="F6" s="312"/>
-      <c r="G6" s="312"/>
-      <c r="H6" s="312"/>
-      <c r="I6" s="312"/>
-      <c r="J6" s="312"/>
-      <c r="K6" s="312"/>
-      <c r="L6" s="312"/>
-      <c r="M6" s="312"/>
-      <c r="N6" s="312"/>
-      <c r="O6" s="312"/>
-      <c r="P6" s="312"/>
-      <c r="Q6" s="312"/>
-      <c r="R6" s="312"/>
-      <c r="S6" s="312"/>
-      <c r="T6" s="312"/>
-      <c r="U6" s="312"/>
-      <c r="V6" s="312"/>
-      <c r="W6" s="312"/>
-      <c r="X6" s="312"/>
-      <c r="Y6" s="312"/>
-      <c r="Z6" s="312"/>
-      <c r="AA6" s="312"/>
-      <c r="AB6" s="312"/>
-      <c r="AC6" s="312"/>
-      <c r="AD6" s="312"/>
-      <c r="AE6" s="312"/>
-      <c r="AF6" s="312"/>
-      <c r="AG6" s="312"/>
-      <c r="AH6" s="312"/>
-      <c r="AI6" s="312"/>
-      <c r="AJ6" s="312"/>
-      <c r="AK6" s="312"/>
-      <c r="AL6" s="312"/>
-      <c r="AM6" s="312"/>
-      <c r="AN6" s="312"/>
-      <c r="AO6" s="312"/>
-      <c r="AP6" s="312"/>
-      <c r="AQ6" s="312"/>
-      <c r="AR6" s="312"/>
-      <c r="AS6" s="312"/>
-      <c r="AT6" s="312"/>
-      <c r="AU6" s="312"/>
-      <c r="AV6" s="312"/>
-      <c r="AW6" s="312"/>
-      <c r="AX6" s="312"/>
-      <c r="AY6" s="313"/>
+      <c r="B6" s="365"/>
+      <c r="C6" s="365"/>
+      <c r="D6" s="365"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
+      <c r="G6" s="365"/>
+      <c r="H6" s="365"/>
+      <c r="I6" s="365"/>
+      <c r="J6" s="365"/>
+      <c r="K6" s="365"/>
+      <c r="L6" s="365"/>
+      <c r="M6" s="365"/>
+      <c r="N6" s="365"/>
+      <c r="O6" s="365"/>
+      <c r="P6" s="365"/>
+      <c r="Q6" s="365"/>
+      <c r="R6" s="365"/>
+      <c r="S6" s="365"/>
+      <c r="T6" s="365"/>
+      <c r="U6" s="365"/>
+      <c r="V6" s="365"/>
+      <c r="W6" s="365"/>
+      <c r="X6" s="365"/>
+      <c r="Y6" s="365"/>
+      <c r="Z6" s="365"/>
+      <c r="AA6" s="365"/>
+      <c r="AB6" s="365"/>
+      <c r="AC6" s="365"/>
+      <c r="AD6" s="365"/>
+      <c r="AE6" s="365"/>
+      <c r="AF6" s="365"/>
+      <c r="AG6" s="365"/>
+      <c r="AH6" s="365"/>
+      <c r="AI6" s="365"/>
+      <c r="AJ6" s="365"/>
+      <c r="AK6" s="365"/>
+      <c r="AL6" s="365"/>
+      <c r="AM6" s="365"/>
+      <c r="AN6" s="365"/>
+      <c r="AO6" s="365"/>
+      <c r="AP6" s="365"/>
+      <c r="AQ6" s="365"/>
+      <c r="AR6" s="365"/>
+      <c r="AS6" s="365"/>
+      <c r="AT6" s="365"/>
+      <c r="AU6" s="365"/>
+      <c r="AV6" s="365"/>
+      <c r="AW6" s="365"/>
+      <c r="AX6" s="365"/>
+      <c r="AY6" s="366"/>
     </row>
     <row r="7" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A7" s="311"/>
-      <c r="B7" s="312"/>
-      <c r="C7" s="312"/>
-      <c r="D7" s="312"/>
-      <c r="E7" s="312"/>
-      <c r="F7" s="312"/>
-      <c r="G7" s="312"/>
-      <c r="H7" s="312"/>
-      <c r="I7" s="312"/>
-      <c r="J7" s="312"/>
-      <c r="K7" s="312"/>
-      <c r="L7" s="312"/>
-      <c r="M7" s="312"/>
-      <c r="N7" s="312"/>
-      <c r="O7" s="312"/>
-      <c r="P7" s="312"/>
-      <c r="Q7" s="312"/>
-      <c r="R7" s="312"/>
-      <c r="S7" s="312"/>
-      <c r="T7" s="312"/>
-      <c r="U7" s="312"/>
-      <c r="V7" s="312"/>
-      <c r="W7" s="312"/>
-      <c r="X7" s="312"/>
-      <c r="Y7" s="312"/>
-      <c r="Z7" s="312"/>
-      <c r="AA7" s="312"/>
-      <c r="AB7" s="312"/>
-      <c r="AC7" s="312"/>
-      <c r="AD7" s="312"/>
-      <c r="AE7" s="312"/>
-      <c r="AF7" s="312"/>
-      <c r="AG7" s="312"/>
-      <c r="AH7" s="312"/>
-      <c r="AI7" s="312"/>
-      <c r="AJ7" s="312"/>
-      <c r="AK7" s="312"/>
-      <c r="AL7" s="312"/>
-      <c r="AM7" s="312"/>
-      <c r="AN7" s="312"/>
-      <c r="AO7" s="312"/>
-      <c r="AP7" s="312"/>
-      <c r="AQ7" s="312"/>
-      <c r="AR7" s="312"/>
-      <c r="AS7" s="312"/>
-      <c r="AT7" s="312"/>
-      <c r="AU7" s="312"/>
-      <c r="AV7" s="312"/>
-      <c r="AW7" s="312"/>
-      <c r="AX7" s="312"/>
-      <c r="AY7" s="313"/>
+      <c r="A7" s="364"/>
+      <c r="B7" s="365"/>
+      <c r="C7" s="365"/>
+      <c r="D7" s="365"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
+      <c r="G7" s="365"/>
+      <c r="H7" s="365"/>
+      <c r="I7" s="365"/>
+      <c r="J7" s="365"/>
+      <c r="K7" s="365"/>
+      <c r="L7" s="365"/>
+      <c r="M7" s="365"/>
+      <c r="N7" s="365"/>
+      <c r="O7" s="365"/>
+      <c r="P7" s="365"/>
+      <c r="Q7" s="365"/>
+      <c r="R7" s="365"/>
+      <c r="S7" s="365"/>
+      <c r="T7" s="365"/>
+      <c r="U7" s="365"/>
+      <c r="V7" s="365"/>
+      <c r="W7" s="365"/>
+      <c r="X7" s="365"/>
+      <c r="Y7" s="365"/>
+      <c r="Z7" s="365"/>
+      <c r="AA7" s="365"/>
+      <c r="AB7" s="365"/>
+      <c r="AC7" s="365"/>
+      <c r="AD7" s="365"/>
+      <c r="AE7" s="365"/>
+      <c r="AF7" s="365"/>
+      <c r="AG7" s="365"/>
+      <c r="AH7" s="365"/>
+      <c r="AI7" s="365"/>
+      <c r="AJ7" s="365"/>
+      <c r="AK7" s="365"/>
+      <c r="AL7" s="365"/>
+      <c r="AM7" s="365"/>
+      <c r="AN7" s="365"/>
+      <c r="AO7" s="365"/>
+      <c r="AP7" s="365"/>
+      <c r="AQ7" s="365"/>
+      <c r="AR7" s="365"/>
+      <c r="AS7" s="365"/>
+      <c r="AT7" s="365"/>
+      <c r="AU7" s="365"/>
+      <c r="AV7" s="365"/>
+      <c r="AW7" s="365"/>
+      <c r="AX7" s="365"/>
+      <c r="AY7" s="366"/>
     </row>
     <row r="8" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A8" s="311"/>
-      <c r="B8" s="312"/>
-      <c r="C8" s="312"/>
-      <c r="D8" s="312"/>
-      <c r="E8" s="312"/>
-      <c r="F8" s="312"/>
-      <c r="G8" s="312"/>
-      <c r="H8" s="312"/>
-      <c r="I8" s="312"/>
-      <c r="J8" s="312"/>
-      <c r="K8" s="312"/>
-      <c r="L8" s="312"/>
-      <c r="M8" s="312"/>
-      <c r="N8" s="312"/>
-      <c r="O8" s="312"/>
-      <c r="P8" s="312"/>
-      <c r="Q8" s="312"/>
-      <c r="R8" s="312"/>
-      <c r="S8" s="312"/>
-      <c r="T8" s="312"/>
-      <c r="U8" s="312"/>
-      <c r="V8" s="312"/>
-      <c r="W8" s="312"/>
-      <c r="X8" s="312"/>
-      <c r="Y8" s="312"/>
-      <c r="Z8" s="312"/>
-      <c r="AA8" s="312"/>
-      <c r="AB8" s="312"/>
-      <c r="AC8" s="312"/>
-      <c r="AD8" s="312"/>
-      <c r="AE8" s="312"/>
-      <c r="AF8" s="312"/>
-      <c r="AG8" s="312"/>
-      <c r="AH8" s="312"/>
-      <c r="AI8" s="312"/>
-      <c r="AJ8" s="312"/>
-      <c r="AK8" s="312"/>
-      <c r="AL8" s="312"/>
-      <c r="AM8" s="312"/>
-      <c r="AN8" s="312"/>
-      <c r="AO8" s="312"/>
-      <c r="AP8" s="312"/>
-      <c r="AQ8" s="312"/>
-      <c r="AR8" s="312"/>
-      <c r="AS8" s="312"/>
-      <c r="AT8" s="312"/>
-      <c r="AU8" s="312"/>
-      <c r="AV8" s="312"/>
-      <c r="AW8" s="312"/>
-      <c r="AX8" s="312"/>
-      <c r="AY8" s="313"/>
-      <c r="BF8" s="192"/>
+      <c r="A8" s="364"/>
+      <c r="B8" s="365"/>
+      <c r="C8" s="365"/>
+      <c r="D8" s="365"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
+      <c r="G8" s="365"/>
+      <c r="H8" s="365"/>
+      <c r="I8" s="365"/>
+      <c r="J8" s="365"/>
+      <c r="K8" s="365"/>
+      <c r="L8" s="365"/>
+      <c r="M8" s="365"/>
+      <c r="N8" s="365"/>
+      <c r="O8" s="365"/>
+      <c r="P8" s="365"/>
+      <c r="Q8" s="365"/>
+      <c r="R8" s="365"/>
+      <c r="S8" s="365"/>
+      <c r="T8" s="365"/>
+      <c r="U8" s="365"/>
+      <c r="V8" s="365"/>
+      <c r="W8" s="365"/>
+      <c r="X8" s="365"/>
+      <c r="Y8" s="365"/>
+      <c r="Z8" s="365"/>
+      <c r="AA8" s="365"/>
+      <c r="AB8" s="365"/>
+      <c r="AC8" s="365"/>
+      <c r="AD8" s="365"/>
+      <c r="AE8" s="365"/>
+      <c r="AF8" s="365"/>
+      <c r="AG8" s="365"/>
+      <c r="AH8" s="365"/>
+      <c r="AI8" s="365"/>
+      <c r="AJ8" s="365"/>
+      <c r="AK8" s="365"/>
+      <c r="AL8" s="365"/>
+      <c r="AM8" s="365"/>
+      <c r="AN8" s="365"/>
+      <c r="AO8" s="365"/>
+      <c r="AP8" s="365"/>
+      <c r="AQ8" s="365"/>
+      <c r="AR8" s="365"/>
+      <c r="AS8" s="365"/>
+      <c r="AT8" s="365"/>
+      <c r="AU8" s="365"/>
+      <c r="AV8" s="365"/>
+      <c r="AW8" s="365"/>
+      <c r="AX8" s="365"/>
+      <c r="AY8" s="366"/>
+      <c r="BF8" s="187"/>
     </row>
     <row r="9" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A9" s="311"/>
-      <c r="B9" s="312"/>
-      <c r="C9" s="312"/>
-      <c r="D9" s="312"/>
-      <c r="E9" s="312"/>
-      <c r="F9" s="312"/>
-      <c r="G9" s="312"/>
-      <c r="H9" s="312"/>
-      <c r="I9" s="312"/>
-      <c r="J9" s="312"/>
-      <c r="K9" s="312"/>
-      <c r="L9" s="312"/>
-      <c r="M9" s="312"/>
-      <c r="N9" s="312"/>
-      <c r="O9" s="312"/>
-      <c r="P9" s="312"/>
-      <c r="Q9" s="312"/>
-      <c r="R9" s="312"/>
-      <c r="S9" s="312"/>
-      <c r="T9" s="312"/>
-      <c r="U9" s="312"/>
-      <c r="V9" s="312"/>
-      <c r="W9" s="312"/>
-      <c r="X9" s="312"/>
-      <c r="Y9" s="312"/>
-      <c r="Z9" s="312"/>
-      <c r="AA9" s="312"/>
-      <c r="AB9" s="312"/>
-      <c r="AC9" s="312"/>
-      <c r="AD9" s="312"/>
-      <c r="AE9" s="312"/>
-      <c r="AF9" s="312"/>
-      <c r="AG9" s="312"/>
-      <c r="AH9" s="312"/>
-      <c r="AI9" s="312"/>
-      <c r="AJ9" s="312"/>
-      <c r="AK9" s="312"/>
-      <c r="AL9" s="312"/>
-      <c r="AM9" s="312"/>
-      <c r="AN9" s="312"/>
-      <c r="AO9" s="312"/>
-      <c r="AP9" s="312"/>
-      <c r="AQ9" s="312"/>
-      <c r="AR9" s="312"/>
-      <c r="AS9" s="312"/>
-      <c r="AT9" s="312"/>
-      <c r="AU9" s="312"/>
-      <c r="AV9" s="312"/>
-      <c r="AW9" s="312"/>
-      <c r="AX9" s="312"/>
-      <c r="AY9" s="313"/>
+      <c r="A9" s="364"/>
+      <c r="B9" s="365"/>
+      <c r="C9" s="365"/>
+      <c r="D9" s="365"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
+      <c r="G9" s="365"/>
+      <c r="H9" s="365"/>
+      <c r="I9" s="365"/>
+      <c r="J9" s="365"/>
+      <c r="K9" s="365"/>
+      <c r="L9" s="365"/>
+      <c r="M9" s="365"/>
+      <c r="N9" s="365"/>
+      <c r="O9" s="365"/>
+      <c r="P9" s="365"/>
+      <c r="Q9" s="365"/>
+      <c r="R9" s="365"/>
+      <c r="S9" s="365"/>
+      <c r="T9" s="365"/>
+      <c r="U9" s="365"/>
+      <c r="V9" s="365"/>
+      <c r="W9" s="365"/>
+      <c r="X9" s="365"/>
+      <c r="Y9" s="365"/>
+      <c r="Z9" s="365"/>
+      <c r="AA9" s="365"/>
+      <c r="AB9" s="365"/>
+      <c r="AC9" s="365"/>
+      <c r="AD9" s="365"/>
+      <c r="AE9" s="365"/>
+      <c r="AF9" s="365"/>
+      <c r="AG9" s="365"/>
+      <c r="AH9" s="365"/>
+      <c r="AI9" s="365"/>
+      <c r="AJ9" s="365"/>
+      <c r="AK9" s="365"/>
+      <c r="AL9" s="365"/>
+      <c r="AM9" s="365"/>
+      <c r="AN9" s="365"/>
+      <c r="AO9" s="365"/>
+      <c r="AP9" s="365"/>
+      <c r="AQ9" s="365"/>
+      <c r="AR9" s="365"/>
+      <c r="AS9" s="365"/>
+      <c r="AT9" s="365"/>
+      <c r="AU9" s="365"/>
+      <c r="AV9" s="365"/>
+      <c r="AW9" s="365"/>
+      <c r="AX9" s="365"/>
+      <c r="AY9" s="366"/>
     </row>
     <row r="10" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A10" s="311"/>
-      <c r="B10" s="312"/>
-      <c r="C10" s="312"/>
-      <c r="D10" s="312"/>
-      <c r="E10" s="312"/>
-      <c r="F10" s="312"/>
-      <c r="G10" s="312"/>
-      <c r="H10" s="312"/>
-      <c r="I10" s="312"/>
-      <c r="J10" s="312"/>
-      <c r="K10" s="312"/>
-      <c r="L10" s="312"/>
-      <c r="M10" s="312"/>
-      <c r="N10" s="312"/>
-      <c r="O10" s="312"/>
-      <c r="P10" s="312"/>
-      <c r="Q10" s="312"/>
-      <c r="R10" s="312"/>
-      <c r="S10" s="312"/>
-      <c r="T10" s="312"/>
-      <c r="U10" s="312"/>
-      <c r="V10" s="312"/>
-      <c r="W10" s="312"/>
-      <c r="X10" s="312"/>
-      <c r="Y10" s="312"/>
-      <c r="Z10" s="312"/>
-      <c r="AA10" s="312"/>
-      <c r="AB10" s="312"/>
-      <c r="AC10" s="312"/>
-      <c r="AD10" s="312"/>
-      <c r="AE10" s="312"/>
-      <c r="AF10" s="312"/>
-      <c r="AG10" s="312"/>
-      <c r="AH10" s="312"/>
-      <c r="AI10" s="312"/>
-      <c r="AJ10" s="312"/>
-      <c r="AK10" s="312"/>
-      <c r="AL10" s="312"/>
-      <c r="AM10" s="312"/>
-      <c r="AN10" s="312"/>
-      <c r="AO10" s="312"/>
-      <c r="AP10" s="312"/>
-      <c r="AQ10" s="312"/>
-      <c r="AR10" s="312"/>
-      <c r="AS10" s="312"/>
-      <c r="AT10" s="312"/>
-      <c r="AU10" s="312"/>
-      <c r="AV10" s="312"/>
-      <c r="AW10" s="312"/>
-      <c r="AX10" s="312"/>
-      <c r="AY10" s="313"/>
+      <c r="A10" s="364"/>
+      <c r="B10" s="365"/>
+      <c r="C10" s="365"/>
+      <c r="D10" s="365"/>
+      <c r="E10" s="365"/>
+      <c r="F10" s="365"/>
+      <c r="G10" s="365"/>
+      <c r="H10" s="365"/>
+      <c r="I10" s="365"/>
+      <c r="J10" s="365"/>
+      <c r="K10" s="365"/>
+      <c r="L10" s="365"/>
+      <c r="M10" s="365"/>
+      <c r="N10" s="365"/>
+      <c r="O10" s="365"/>
+      <c r="P10" s="365"/>
+      <c r="Q10" s="365"/>
+      <c r="R10" s="365"/>
+      <c r="S10" s="365"/>
+      <c r="T10" s="365"/>
+      <c r="U10" s="365"/>
+      <c r="V10" s="365"/>
+      <c r="W10" s="365"/>
+      <c r="X10" s="365"/>
+      <c r="Y10" s="365"/>
+      <c r="Z10" s="365"/>
+      <c r="AA10" s="365"/>
+      <c r="AB10" s="365"/>
+      <c r="AC10" s="365"/>
+      <c r="AD10" s="365"/>
+      <c r="AE10" s="365"/>
+      <c r="AF10" s="365"/>
+      <c r="AG10" s="365"/>
+      <c r="AH10" s="365"/>
+      <c r="AI10" s="365"/>
+      <c r="AJ10" s="365"/>
+      <c r="AK10" s="365"/>
+      <c r="AL10" s="365"/>
+      <c r="AM10" s="365"/>
+      <c r="AN10" s="365"/>
+      <c r="AO10" s="365"/>
+      <c r="AP10" s="365"/>
+      <c r="AQ10" s="365"/>
+      <c r="AR10" s="365"/>
+      <c r="AS10" s="365"/>
+      <c r="AT10" s="365"/>
+      <c r="AU10" s="365"/>
+      <c r="AV10" s="365"/>
+      <c r="AW10" s="365"/>
+      <c r="AX10" s="365"/>
+      <c r="AY10" s="366"/>
     </row>
     <row r="11" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A11" s="314" t="s">
+      <c r="A11" s="367" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="315"/>
-      <c r="C11" s="315"/>
-      <c r="D11" s="315"/>
-      <c r="E11" s="315"/>
-      <c r="F11" s="315"/>
-      <c r="G11" s="315"/>
-      <c r="H11" s="315"/>
-      <c r="I11" s="315"/>
-      <c r="J11" s="315"/>
-      <c r="K11" s="315"/>
-      <c r="L11" s="315"/>
-      <c r="M11" s="315"/>
-      <c r="N11" s="315"/>
-      <c r="O11" s="315"/>
-      <c r="P11" s="315"/>
-      <c r="Q11" s="315"/>
-      <c r="R11" s="315"/>
-      <c r="S11" s="315"/>
-      <c r="T11" s="315"/>
-      <c r="U11" s="315"/>
-      <c r="V11" s="315"/>
-      <c r="W11" s="315"/>
-      <c r="X11" s="315"/>
-      <c r="Y11" s="315"/>
-      <c r="Z11" s="315"/>
-      <c r="AA11" s="315"/>
-      <c r="AB11" s="315"/>
-      <c r="AC11" s="315"/>
-      <c r="AD11" s="315"/>
-      <c r="AE11" s="315"/>
-      <c r="AF11" s="315"/>
-      <c r="AG11" s="315"/>
-      <c r="AH11" s="315"/>
-      <c r="AI11" s="315"/>
-      <c r="AJ11" s="315"/>
-      <c r="AK11" s="315"/>
-      <c r="AL11" s="315"/>
-      <c r="AM11" s="315"/>
-      <c r="AN11" s="315"/>
-      <c r="AO11" s="315"/>
-      <c r="AP11" s="315"/>
-      <c r="AQ11" s="315"/>
-      <c r="AR11" s="315"/>
-      <c r="AS11" s="315"/>
-      <c r="AT11" s="315"/>
-      <c r="AU11" s="315"/>
-      <c r="AV11" s="315"/>
-      <c r="AW11" s="315"/>
-      <c r="AX11" s="315"/>
-      <c r="AY11" s="316"/>
+      <c r="B11" s="368"/>
+      <c r="C11" s="368"/>
+      <c r="D11" s="368"/>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
+      <c r="G11" s="368"/>
+      <c r="H11" s="368"/>
+      <c r="I11" s="368"/>
+      <c r="J11" s="368"/>
+      <c r="K11" s="368"/>
+      <c r="L11" s="368"/>
+      <c r="M11" s="368"/>
+      <c r="N11" s="368"/>
+      <c r="O11" s="368"/>
+      <c r="P11" s="368"/>
+      <c r="Q11" s="368"/>
+      <c r="R11" s="368"/>
+      <c r="S11" s="368"/>
+      <c r="T11" s="368"/>
+      <c r="U11" s="368"/>
+      <c r="V11" s="368"/>
+      <c r="W11" s="368"/>
+      <c r="X11" s="368"/>
+      <c r="Y11" s="368"/>
+      <c r="Z11" s="368"/>
+      <c r="AA11" s="368"/>
+      <c r="AB11" s="368"/>
+      <c r="AC11" s="368"/>
+      <c r="AD11" s="368"/>
+      <c r="AE11" s="368"/>
+      <c r="AF11" s="368"/>
+      <c r="AG11" s="368"/>
+      <c r="AH11" s="368"/>
+      <c r="AI11" s="368"/>
+      <c r="AJ11" s="368"/>
+      <c r="AK11" s="368"/>
+      <c r="AL11" s="368"/>
+      <c r="AM11" s="368"/>
+      <c r="AN11" s="368"/>
+      <c r="AO11" s="368"/>
+      <c r="AP11" s="368"/>
+      <c r="AQ11" s="368"/>
+      <c r="AR11" s="368"/>
+      <c r="AS11" s="368"/>
+      <c r="AT11" s="368"/>
+      <c r="AU11" s="368"/>
+      <c r="AV11" s="368"/>
+      <c r="AW11" s="368"/>
+      <c r="AX11" s="368"/>
+      <c r="AY11" s="369"/>
     </row>
     <row r="12" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A12" s="314"/>
-      <c r="B12" s="315"/>
-      <c r="C12" s="315"/>
-      <c r="D12" s="315"/>
-      <c r="E12" s="315"/>
-      <c r="F12" s="315"/>
-      <c r="G12" s="315"/>
-      <c r="H12" s="315"/>
-      <c r="I12" s="315"/>
-      <c r="J12" s="315"/>
-      <c r="K12" s="315"/>
-      <c r="L12" s="315"/>
-      <c r="M12" s="315"/>
-      <c r="N12" s="315"/>
-      <c r="O12" s="315"/>
-      <c r="P12" s="315"/>
-      <c r="Q12" s="315"/>
-      <c r="R12" s="315"/>
-      <c r="S12" s="315"/>
-      <c r="T12" s="315"/>
-      <c r="U12" s="315"/>
-      <c r="V12" s="315"/>
-      <c r="W12" s="315"/>
-      <c r="X12" s="315"/>
-      <c r="Y12" s="315"/>
-      <c r="Z12" s="315"/>
-      <c r="AA12" s="315"/>
-      <c r="AB12" s="315"/>
-      <c r="AC12" s="315"/>
-      <c r="AD12" s="315"/>
-      <c r="AE12" s="315"/>
-      <c r="AF12" s="315"/>
-      <c r="AG12" s="315"/>
-      <c r="AH12" s="315"/>
-      <c r="AI12" s="315"/>
-      <c r="AJ12" s="315"/>
-      <c r="AK12" s="315"/>
-      <c r="AL12" s="315"/>
-      <c r="AM12" s="315"/>
-      <c r="AN12" s="315"/>
-      <c r="AO12" s="315"/>
-      <c r="AP12" s="315"/>
-      <c r="AQ12" s="315"/>
-      <c r="AR12" s="315"/>
-      <c r="AS12" s="315"/>
-      <c r="AT12" s="315"/>
-      <c r="AU12" s="315"/>
-      <c r="AV12" s="315"/>
-      <c r="AW12" s="315"/>
-      <c r="AX12" s="315"/>
-      <c r="AY12" s="316"/>
+      <c r="A12" s="367"/>
+      <c r="B12" s="368"/>
+      <c r="C12" s="368"/>
+      <c r="D12" s="368"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
+      <c r="G12" s="368"/>
+      <c r="H12" s="368"/>
+      <c r="I12" s="368"/>
+      <c r="J12" s="368"/>
+      <c r="K12" s="368"/>
+      <c r="L12" s="368"/>
+      <c r="M12" s="368"/>
+      <c r="N12" s="368"/>
+      <c r="O12" s="368"/>
+      <c r="P12" s="368"/>
+      <c r="Q12" s="368"/>
+      <c r="R12" s="368"/>
+      <c r="S12" s="368"/>
+      <c r="T12" s="368"/>
+      <c r="U12" s="368"/>
+      <c r="V12" s="368"/>
+      <c r="W12" s="368"/>
+      <c r="X12" s="368"/>
+      <c r="Y12" s="368"/>
+      <c r="Z12" s="368"/>
+      <c r="AA12" s="368"/>
+      <c r="AB12" s="368"/>
+      <c r="AC12" s="368"/>
+      <c r="AD12" s="368"/>
+      <c r="AE12" s="368"/>
+      <c r="AF12" s="368"/>
+      <c r="AG12" s="368"/>
+      <c r="AH12" s="368"/>
+      <c r="AI12" s="368"/>
+      <c r="AJ12" s="368"/>
+      <c r="AK12" s="368"/>
+      <c r="AL12" s="368"/>
+      <c r="AM12" s="368"/>
+      <c r="AN12" s="368"/>
+      <c r="AO12" s="368"/>
+      <c r="AP12" s="368"/>
+      <c r="AQ12" s="368"/>
+      <c r="AR12" s="368"/>
+      <c r="AS12" s="368"/>
+      <c r="AT12" s="368"/>
+      <c r="AU12" s="368"/>
+      <c r="AV12" s="368"/>
+      <c r="AW12" s="368"/>
+      <c r="AX12" s="368"/>
+      <c r="AY12" s="369"/>
     </row>
     <row r="13" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A13" s="314"/>
-      <c r="B13" s="315"/>
-      <c r="C13" s="315"/>
-      <c r="D13" s="315"/>
-      <c r="E13" s="315"/>
-      <c r="F13" s="315"/>
-      <c r="G13" s="315"/>
-      <c r="H13" s="315"/>
-      <c r="I13" s="315"/>
-      <c r="J13" s="315"/>
-      <c r="K13" s="315"/>
-      <c r="L13" s="315"/>
-      <c r="M13" s="315"/>
-      <c r="N13" s="315"/>
-      <c r="O13" s="315"/>
-      <c r="P13" s="315"/>
-      <c r="Q13" s="315"/>
-      <c r="R13" s="315"/>
-      <c r="S13" s="315"/>
-      <c r="T13" s="315"/>
-      <c r="U13" s="315"/>
-      <c r="V13" s="315"/>
-      <c r="W13" s="315"/>
-      <c r="X13" s="315"/>
-      <c r="Y13" s="315"/>
-      <c r="Z13" s="315"/>
-      <c r="AA13" s="315"/>
-      <c r="AB13" s="315"/>
-      <c r="AC13" s="315"/>
-      <c r="AD13" s="315"/>
-      <c r="AE13" s="315"/>
-      <c r="AF13" s="315"/>
-      <c r="AG13" s="315"/>
-      <c r="AH13" s="315"/>
-      <c r="AI13" s="315"/>
-      <c r="AJ13" s="315"/>
-      <c r="AK13" s="315"/>
-      <c r="AL13" s="315"/>
-      <c r="AM13" s="315"/>
-      <c r="AN13" s="315"/>
-      <c r="AO13" s="315"/>
-      <c r="AP13" s="315"/>
-      <c r="AQ13" s="315"/>
-      <c r="AR13" s="315"/>
-      <c r="AS13" s="315"/>
-      <c r="AT13" s="315"/>
-      <c r="AU13" s="315"/>
-      <c r="AV13" s="315"/>
-      <c r="AW13" s="315"/>
-      <c r="AX13" s="315"/>
-      <c r="AY13" s="316"/>
+      <c r="A13" s="367"/>
+      <c r="B13" s="368"/>
+      <c r="C13" s="368"/>
+      <c r="D13" s="368"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
+      <c r="G13" s="368"/>
+      <c r="H13" s="368"/>
+      <c r="I13" s="368"/>
+      <c r="J13" s="368"/>
+      <c r="K13" s="368"/>
+      <c r="L13" s="368"/>
+      <c r="M13" s="368"/>
+      <c r="N13" s="368"/>
+      <c r="O13" s="368"/>
+      <c r="P13" s="368"/>
+      <c r="Q13" s="368"/>
+      <c r="R13" s="368"/>
+      <c r="S13" s="368"/>
+      <c r="T13" s="368"/>
+      <c r="U13" s="368"/>
+      <c r="V13" s="368"/>
+      <c r="W13" s="368"/>
+      <c r="X13" s="368"/>
+      <c r="Y13" s="368"/>
+      <c r="Z13" s="368"/>
+      <c r="AA13" s="368"/>
+      <c r="AB13" s="368"/>
+      <c r="AC13" s="368"/>
+      <c r="AD13" s="368"/>
+      <c r="AE13" s="368"/>
+      <c r="AF13" s="368"/>
+      <c r="AG13" s="368"/>
+      <c r="AH13" s="368"/>
+      <c r="AI13" s="368"/>
+      <c r="AJ13" s="368"/>
+      <c r="AK13" s="368"/>
+      <c r="AL13" s="368"/>
+      <c r="AM13" s="368"/>
+      <c r="AN13" s="368"/>
+      <c r="AO13" s="368"/>
+      <c r="AP13" s="368"/>
+      <c r="AQ13" s="368"/>
+      <c r="AR13" s="368"/>
+      <c r="AS13" s="368"/>
+      <c r="AT13" s="368"/>
+      <c r="AU13" s="368"/>
+      <c r="AV13" s="368"/>
+      <c r="AW13" s="368"/>
+      <c r="AX13" s="368"/>
+      <c r="AY13" s="369"/>
     </row>
     <row r="14" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A14" s="311" t="s">
+      <c r="A14" s="364" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="315"/>
-      <c r="C14" s="315"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
-      <c r="G14" s="315"/>
-      <c r="H14" s="315"/>
-      <c r="I14" s="315"/>
-      <c r="J14" s="315"/>
-      <c r="K14" s="315"/>
-      <c r="L14" s="315"/>
-      <c r="M14" s="315"/>
-      <c r="N14" s="315"/>
-      <c r="O14" s="315"/>
-      <c r="P14" s="315"/>
-      <c r="Q14" s="315"/>
-      <c r="R14" s="315"/>
-      <c r="S14" s="315"/>
-      <c r="T14" s="315"/>
-      <c r="U14" s="315"/>
-      <c r="V14" s="315"/>
-      <c r="W14" s="315"/>
-      <c r="X14" s="315"/>
-      <c r="Y14" s="315"/>
-      <c r="Z14" s="315"/>
-      <c r="AA14" s="315"/>
-      <c r="AB14" s="315"/>
-      <c r="AC14" s="315"/>
-      <c r="AD14" s="315"/>
-      <c r="AE14" s="315"/>
-      <c r="AF14" s="315"/>
-      <c r="AG14" s="315"/>
-      <c r="AH14" s="315"/>
-      <c r="AI14" s="315"/>
-      <c r="AJ14" s="315"/>
-      <c r="AK14" s="315"/>
-      <c r="AL14" s="315"/>
-      <c r="AM14" s="315"/>
-      <c r="AN14" s="315"/>
-      <c r="AO14" s="315"/>
-      <c r="AP14" s="315"/>
-      <c r="AQ14" s="315"/>
-      <c r="AR14" s="315"/>
-      <c r="AS14" s="315"/>
-      <c r="AT14" s="315"/>
-      <c r="AU14" s="315"/>
-      <c r="AV14" s="315"/>
-      <c r="AW14" s="315"/>
-      <c r="AX14" s="315"/>
-      <c r="AY14" s="316"/>
+      <c r="B14" s="368"/>
+      <c r="C14" s="368"/>
+      <c r="D14" s="368"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
+      <c r="G14" s="368"/>
+      <c r="H14" s="368"/>
+      <c r="I14" s="368"/>
+      <c r="J14" s="368"/>
+      <c r="K14" s="368"/>
+      <c r="L14" s="368"/>
+      <c r="M14" s="368"/>
+      <c r="N14" s="368"/>
+      <c r="O14" s="368"/>
+      <c r="P14" s="368"/>
+      <c r="Q14" s="368"/>
+      <c r="R14" s="368"/>
+      <c r="S14" s="368"/>
+      <c r="T14" s="368"/>
+      <c r="U14" s="368"/>
+      <c r="V14" s="368"/>
+      <c r="W14" s="368"/>
+      <c r="X14" s="368"/>
+      <c r="Y14" s="368"/>
+      <c r="Z14" s="368"/>
+      <c r="AA14" s="368"/>
+      <c r="AB14" s="368"/>
+      <c r="AC14" s="368"/>
+      <c r="AD14" s="368"/>
+      <c r="AE14" s="368"/>
+      <c r="AF14" s="368"/>
+      <c r="AG14" s="368"/>
+      <c r="AH14" s="368"/>
+      <c r="AI14" s="368"/>
+      <c r="AJ14" s="368"/>
+      <c r="AK14" s="368"/>
+      <c r="AL14" s="368"/>
+      <c r="AM14" s="368"/>
+      <c r="AN14" s="368"/>
+      <c r="AO14" s="368"/>
+      <c r="AP14" s="368"/>
+      <c r="AQ14" s="368"/>
+      <c r="AR14" s="368"/>
+      <c r="AS14" s="368"/>
+      <c r="AT14" s="368"/>
+      <c r="AU14" s="368"/>
+      <c r="AV14" s="368"/>
+      <c r="AW14" s="368"/>
+      <c r="AX14" s="368"/>
+      <c r="AY14" s="369"/>
     </row>
     <row r="15" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A15" s="314"/>
-      <c r="B15" s="315"/>
-      <c r="C15" s="315"/>
-      <c r="D15" s="315"/>
-      <c r="E15" s="315"/>
-      <c r="F15" s="315"/>
-      <c r="G15" s="315"/>
-      <c r="H15" s="315"/>
-      <c r="I15" s="315"/>
-      <c r="J15" s="315"/>
-      <c r="K15" s="315"/>
-      <c r="L15" s="315"/>
-      <c r="M15" s="315"/>
-      <c r="N15" s="315"/>
-      <c r="O15" s="315"/>
-      <c r="P15" s="315"/>
-      <c r="Q15" s="315"/>
-      <c r="R15" s="315"/>
-      <c r="S15" s="315"/>
-      <c r="T15" s="315"/>
-      <c r="U15" s="315"/>
-      <c r="V15" s="315"/>
-      <c r="W15" s="315"/>
-      <c r="X15" s="315"/>
-      <c r="Y15" s="315"/>
-      <c r="Z15" s="315"/>
-      <c r="AA15" s="315"/>
-      <c r="AB15" s="315"/>
-      <c r="AC15" s="315"/>
-      <c r="AD15" s="315"/>
-      <c r="AE15" s="315"/>
-      <c r="AF15" s="315"/>
-      <c r="AG15" s="315"/>
-      <c r="AH15" s="315"/>
-      <c r="AI15" s="315"/>
-      <c r="AJ15" s="315"/>
-      <c r="AK15" s="315"/>
-      <c r="AL15" s="315"/>
-      <c r="AM15" s="315"/>
-      <c r="AN15" s="315"/>
-      <c r="AO15" s="315"/>
-      <c r="AP15" s="315"/>
-      <c r="AQ15" s="315"/>
-      <c r="AR15" s="315"/>
-      <c r="AS15" s="315"/>
-      <c r="AT15" s="315"/>
-      <c r="AU15" s="315"/>
-      <c r="AV15" s="315"/>
-      <c r="AW15" s="315"/>
-      <c r="AX15" s="315"/>
-      <c r="AY15" s="316"/>
+      <c r="A15" s="367"/>
+      <c r="B15" s="368"/>
+      <c r="C15" s="368"/>
+      <c r="D15" s="368"/>
+      <c r="E15" s="368"/>
+      <c r="F15" s="368"/>
+      <c r="G15" s="368"/>
+      <c r="H15" s="368"/>
+      <c r="I15" s="368"/>
+      <c r="J15" s="368"/>
+      <c r="K15" s="368"/>
+      <c r="L15" s="368"/>
+      <c r="M15" s="368"/>
+      <c r="N15" s="368"/>
+      <c r="O15" s="368"/>
+      <c r="P15" s="368"/>
+      <c r="Q15" s="368"/>
+      <c r="R15" s="368"/>
+      <c r="S15" s="368"/>
+      <c r="T15" s="368"/>
+      <c r="U15" s="368"/>
+      <c r="V15" s="368"/>
+      <c r="W15" s="368"/>
+      <c r="X15" s="368"/>
+      <c r="Y15" s="368"/>
+      <c r="Z15" s="368"/>
+      <c r="AA15" s="368"/>
+      <c r="AB15" s="368"/>
+      <c r="AC15" s="368"/>
+      <c r="AD15" s="368"/>
+      <c r="AE15" s="368"/>
+      <c r="AF15" s="368"/>
+      <c r="AG15" s="368"/>
+      <c r="AH15" s="368"/>
+      <c r="AI15" s="368"/>
+      <c r="AJ15" s="368"/>
+      <c r="AK15" s="368"/>
+      <c r="AL15" s="368"/>
+      <c r="AM15" s="368"/>
+      <c r="AN15" s="368"/>
+      <c r="AO15" s="368"/>
+      <c r="AP15" s="368"/>
+      <c r="AQ15" s="368"/>
+      <c r="AR15" s="368"/>
+      <c r="AS15" s="368"/>
+      <c r="AT15" s="368"/>
+      <c r="AU15" s="368"/>
+      <c r="AV15" s="368"/>
+      <c r="AW15" s="368"/>
+      <c r="AX15" s="368"/>
+      <c r="AY15" s="369"/>
     </row>
     <row r="16" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A16" s="314"/>
-      <c r="B16" s="315"/>
-      <c r="C16" s="315"/>
-      <c r="D16" s="315"/>
-      <c r="E16" s="315"/>
-      <c r="F16" s="315"/>
-      <c r="G16" s="315"/>
-      <c r="H16" s="315"/>
-      <c r="I16" s="315"/>
-      <c r="J16" s="315"/>
-      <c r="K16" s="315"/>
-      <c r="L16" s="315"/>
-      <c r="M16" s="315"/>
-      <c r="N16" s="315"/>
-      <c r="O16" s="315"/>
-      <c r="P16" s="315"/>
-      <c r="Q16" s="315"/>
-      <c r="R16" s="315"/>
-      <c r="S16" s="315"/>
-      <c r="T16" s="315"/>
-      <c r="U16" s="315"/>
-      <c r="V16" s="315"/>
-      <c r="W16" s="315"/>
-      <c r="X16" s="315"/>
-      <c r="Y16" s="315"/>
-      <c r="Z16" s="315"/>
-      <c r="AA16" s="315"/>
-      <c r="AB16" s="315"/>
-      <c r="AC16" s="315"/>
-      <c r="AD16" s="315"/>
-      <c r="AE16" s="315"/>
-      <c r="AF16" s="315"/>
-      <c r="AG16" s="315"/>
-      <c r="AH16" s="315"/>
-      <c r="AI16" s="315"/>
-      <c r="AJ16" s="315"/>
-      <c r="AK16" s="315"/>
-      <c r="AL16" s="315"/>
-      <c r="AM16" s="315"/>
-      <c r="AN16" s="315"/>
-      <c r="AO16" s="315"/>
-      <c r="AP16" s="315"/>
-      <c r="AQ16" s="315"/>
-      <c r="AR16" s="315"/>
-      <c r="AS16" s="315"/>
-      <c r="AT16" s="315"/>
-      <c r="AU16" s="315"/>
-      <c r="AV16" s="315"/>
-      <c r="AW16" s="315"/>
-      <c r="AX16" s="315"/>
-      <c r="AY16" s="316"/>
+      <c r="A16" s="367"/>
+      <c r="B16" s="368"/>
+      <c r="C16" s="368"/>
+      <c r="D16" s="368"/>
+      <c r="E16" s="368"/>
+      <c r="F16" s="368"/>
+      <c r="G16" s="368"/>
+      <c r="H16" s="368"/>
+      <c r="I16" s="368"/>
+      <c r="J16" s="368"/>
+      <c r="K16" s="368"/>
+      <c r="L16" s="368"/>
+      <c r="M16" s="368"/>
+      <c r="N16" s="368"/>
+      <c r="O16" s="368"/>
+      <c r="P16" s="368"/>
+      <c r="Q16" s="368"/>
+      <c r="R16" s="368"/>
+      <c r="S16" s="368"/>
+      <c r="T16" s="368"/>
+      <c r="U16" s="368"/>
+      <c r="V16" s="368"/>
+      <c r="W16" s="368"/>
+      <c r="X16" s="368"/>
+      <c r="Y16" s="368"/>
+      <c r="Z16" s="368"/>
+      <c r="AA16" s="368"/>
+      <c r="AB16" s="368"/>
+      <c r="AC16" s="368"/>
+      <c r="AD16" s="368"/>
+      <c r="AE16" s="368"/>
+      <c r="AF16" s="368"/>
+      <c r="AG16" s="368"/>
+      <c r="AH16" s="368"/>
+      <c r="AI16" s="368"/>
+      <c r="AJ16" s="368"/>
+      <c r="AK16" s="368"/>
+      <c r="AL16" s="368"/>
+      <c r="AM16" s="368"/>
+      <c r="AN16" s="368"/>
+      <c r="AO16" s="368"/>
+      <c r="AP16" s="368"/>
+      <c r="AQ16" s="368"/>
+      <c r="AR16" s="368"/>
+      <c r="AS16" s="368"/>
+      <c r="AT16" s="368"/>
+      <c r="AU16" s="368"/>
+      <c r="AV16" s="368"/>
+      <c r="AW16" s="368"/>
+      <c r="AX16" s="368"/>
+      <c r="AY16" s="369"/>
     </row>
     <row r="17" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A17" s="190"/>
-      <c r="AY17" s="191"/>
+      <c r="A17" s="185"/>
+      <c r="AY17" s="186"/>
     </row>
     <row r="18" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A18" s="190"/>
-      <c r="Q18" s="317"/>
-      <c r="R18" s="317"/>
-      <c r="S18" s="317"/>
-      <c r="T18" s="317"/>
-      <c r="U18" s="317"/>
-      <c r="V18" s="317"/>
-      <c r="W18" s="317"/>
-      <c r="X18" s="317"/>
-      <c r="Y18" s="317"/>
-      <c r="Z18" s="317"/>
-      <c r="AA18" s="317"/>
-      <c r="AB18" s="317"/>
-      <c r="AC18" s="317"/>
-      <c r="AD18" s="317"/>
-      <c r="AE18" s="317"/>
-      <c r="AF18" s="317"/>
-      <c r="AG18" s="317"/>
-      <c r="AH18" s="317"/>
-      <c r="AI18" s="317"/>
-      <c r="AJ18" s="317"/>
-      <c r="AY18" s="191"/>
+      <c r="A18" s="185"/>
+      <c r="Q18" s="370"/>
+      <c r="R18" s="370"/>
+      <c r="S18" s="370"/>
+      <c r="T18" s="370"/>
+      <c r="U18" s="370"/>
+      <c r="V18" s="370"/>
+      <c r="W18" s="370"/>
+      <c r="X18" s="370"/>
+      <c r="Y18" s="370"/>
+      <c r="Z18" s="370"/>
+      <c r="AA18" s="370"/>
+      <c r="AB18" s="370"/>
+      <c r="AC18" s="370"/>
+      <c r="AD18" s="370"/>
+      <c r="AE18" s="370"/>
+      <c r="AF18" s="370"/>
+      <c r="AG18" s="370"/>
+      <c r="AH18" s="370"/>
+      <c r="AI18" s="370"/>
+      <c r="AJ18" s="370"/>
+      <c r="AY18" s="186"/>
     </row>
     <row r="19" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A19" s="190"/>
-      <c r="Q19" s="304"/>
-      <c r="R19" s="304"/>
-      <c r="S19" s="304"/>
-      <c r="T19" s="304"/>
-      <c r="U19" s="304"/>
-      <c r="V19" s="304"/>
-      <c r="W19" s="304"/>
-      <c r="X19" s="304"/>
-      <c r="Y19" s="304"/>
-      <c r="Z19" s="304"/>
-      <c r="AA19" s="304"/>
-      <c r="AB19" s="304"/>
-      <c r="AC19" s="304"/>
-      <c r="AD19" s="304"/>
-      <c r="AE19" s="304"/>
-      <c r="AF19" s="304"/>
-      <c r="AG19" s="304"/>
-      <c r="AH19" s="304"/>
-      <c r="AI19" s="304"/>
-      <c r="AJ19" s="304"/>
-      <c r="AY19" s="191"/>
+      <c r="A19" s="185"/>
+      <c r="Q19" s="374"/>
+      <c r="R19" s="374"/>
+      <c r="S19" s="374"/>
+      <c r="T19" s="374"/>
+      <c r="U19" s="374"/>
+      <c r="V19" s="374"/>
+      <c r="W19" s="374"/>
+      <c r="X19" s="374"/>
+      <c r="Y19" s="374"/>
+      <c r="Z19" s="374"/>
+      <c r="AA19" s="374"/>
+      <c r="AB19" s="374"/>
+      <c r="AC19" s="374"/>
+      <c r="AD19" s="374"/>
+      <c r="AE19" s="374"/>
+      <c r="AF19" s="374"/>
+      <c r="AG19" s="374"/>
+      <c r="AH19" s="374"/>
+      <c r="AI19" s="374"/>
+      <c r="AJ19" s="374"/>
+      <c r="AY19" s="186"/>
     </row>
     <row r="20" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A20" s="190"/>
-      <c r="Q20" s="304"/>
-      <c r="R20" s="304"/>
-      <c r="S20" s="304"/>
-      <c r="T20" s="304"/>
-      <c r="U20" s="304"/>
-      <c r="V20" s="304"/>
-      <c r="W20" s="304"/>
-      <c r="X20" s="304"/>
-      <c r="Y20" s="304"/>
-      <c r="Z20" s="304"/>
-      <c r="AA20" s="304"/>
-      <c r="AB20" s="304"/>
-      <c r="AC20" s="304"/>
-      <c r="AD20" s="304"/>
-      <c r="AE20" s="304"/>
-      <c r="AF20" s="304"/>
-      <c r="AG20" s="304"/>
-      <c r="AH20" s="304"/>
-      <c r="AI20" s="304"/>
-      <c r="AJ20" s="304"/>
-      <c r="AY20" s="191"/>
+      <c r="A20" s="185"/>
+      <c r="Q20" s="374"/>
+      <c r="R20" s="374"/>
+      <c r="S20" s="374"/>
+      <c r="T20" s="374"/>
+      <c r="U20" s="374"/>
+      <c r="V20" s="374"/>
+      <c r="W20" s="374"/>
+      <c r="X20" s="374"/>
+      <c r="Y20" s="374"/>
+      <c r="Z20" s="374"/>
+      <c r="AA20" s="374"/>
+      <c r="AB20" s="374"/>
+      <c r="AC20" s="374"/>
+      <c r="AD20" s="374"/>
+      <c r="AE20" s="374"/>
+      <c r="AF20" s="374"/>
+      <c r="AG20" s="374"/>
+      <c r="AH20" s="374"/>
+      <c r="AI20" s="374"/>
+      <c r="AJ20" s="374"/>
+      <c r="AY20" s="186"/>
     </row>
     <row r="21" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A21" s="190"/>
-      <c r="Q21" s="304"/>
-      <c r="R21" s="304"/>
-      <c r="S21" s="304"/>
-      <c r="T21" s="304"/>
-      <c r="U21" s="304"/>
-      <c r="V21" s="304"/>
-      <c r="W21" s="304"/>
-      <c r="X21" s="304"/>
-      <c r="Y21" s="304"/>
-      <c r="Z21" s="304"/>
-      <c r="AA21" s="304"/>
-      <c r="AB21" s="304"/>
-      <c r="AC21" s="304"/>
-      <c r="AD21" s="304"/>
-      <c r="AE21" s="304"/>
-      <c r="AF21" s="304"/>
-      <c r="AG21" s="304"/>
-      <c r="AH21" s="304"/>
-      <c r="AI21" s="304"/>
-      <c r="AJ21" s="304"/>
-      <c r="AY21" s="191"/>
+      <c r="A21" s="185"/>
+      <c r="Q21" s="374"/>
+      <c r="R21" s="374"/>
+      <c r="S21" s="374"/>
+      <c r="T21" s="374"/>
+      <c r="U21" s="374"/>
+      <c r="V21" s="374"/>
+      <c r="W21" s="374"/>
+      <c r="X21" s="374"/>
+      <c r="Y21" s="374"/>
+      <c r="Z21" s="374"/>
+      <c r="AA21" s="374"/>
+      <c r="AB21" s="374"/>
+      <c r="AC21" s="374"/>
+      <c r="AD21" s="374"/>
+      <c r="AE21" s="374"/>
+      <c r="AF21" s="374"/>
+      <c r="AG21" s="374"/>
+      <c r="AH21" s="374"/>
+      <c r="AI21" s="374"/>
+      <c r="AJ21" s="374"/>
+      <c r="AY21" s="186"/>
     </row>
     <row r="22" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A22" s="190"/>
-      <c r="Q22" s="304"/>
-      <c r="R22" s="304"/>
-      <c r="S22" s="304"/>
-      <c r="T22" s="304"/>
-      <c r="U22" s="304"/>
-      <c r="V22" s="304"/>
-      <c r="W22" s="304"/>
-      <c r="X22" s="304"/>
-      <c r="Y22" s="304"/>
-      <c r="Z22" s="304"/>
-      <c r="AA22" s="304"/>
-      <c r="AB22" s="304"/>
-      <c r="AC22" s="304"/>
-      <c r="AD22" s="304"/>
-      <c r="AE22" s="304"/>
-      <c r="AF22" s="304"/>
-      <c r="AG22" s="304"/>
-      <c r="AH22" s="304"/>
-      <c r="AI22" s="304"/>
-      <c r="AJ22" s="304"/>
-      <c r="AY22" s="191"/>
+      <c r="A22" s="185"/>
+      <c r="Q22" s="374"/>
+      <c r="R22" s="374"/>
+      <c r="S22" s="374"/>
+      <c r="T22" s="374"/>
+      <c r="U22" s="374"/>
+      <c r="V22" s="374"/>
+      <c r="W22" s="374"/>
+      <c r="X22" s="374"/>
+      <c r="Y22" s="374"/>
+      <c r="Z22" s="374"/>
+      <c r="AA22" s="374"/>
+      <c r="AB22" s="374"/>
+      <c r="AC22" s="374"/>
+      <c r="AD22" s="374"/>
+      <c r="AE22" s="374"/>
+      <c r="AF22" s="374"/>
+      <c r="AG22" s="374"/>
+      <c r="AH22" s="374"/>
+      <c r="AI22" s="374"/>
+      <c r="AJ22" s="374"/>
+      <c r="AY22" s="186"/>
     </row>
     <row r="23" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A23" s="190"/>
-      <c r="AY23" s="191"/>
+      <c r="A23" s="185"/>
+      <c r="AY23" s="186"/>
     </row>
     <row r="24" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A24" s="190"/>
-      <c r="AY24" s="191"/>
+      <c r="A24" s="185"/>
+      <c r="AY24" s="186"/>
     </row>
     <row r="25" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A25" s="305">
+      <c r="A25" s="375">
         <v>46112</v>
       </c>
-      <c r="B25" s="306"/>
-      <c r="C25" s="306"/>
-      <c r="D25" s="306"/>
-      <c r="E25" s="306"/>
-      <c r="F25" s="306"/>
-      <c r="G25" s="306"/>
-      <c r="H25" s="306"/>
-      <c r="I25" s="306"/>
-      <c r="J25" s="306"/>
-      <c r="K25" s="306"/>
-      <c r="L25" s="306"/>
-      <c r="M25" s="306"/>
-      <c r="N25" s="306"/>
-      <c r="O25" s="306"/>
-      <c r="P25" s="306"/>
-      <c r="Q25" s="306"/>
-      <c r="R25" s="306"/>
-      <c r="S25" s="306"/>
-      <c r="T25" s="306"/>
-      <c r="U25" s="306"/>
-      <c r="V25" s="306"/>
-      <c r="W25" s="306"/>
-      <c r="X25" s="306"/>
-      <c r="Y25" s="306"/>
-      <c r="Z25" s="306"/>
-      <c r="AA25" s="306"/>
-      <c r="AB25" s="306"/>
-      <c r="AC25" s="193"/>
-      <c r="AD25" s="307">
+      <c r="B25" s="376"/>
+      <c r="C25" s="376"/>
+      <c r="D25" s="376"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
+      <c r="G25" s="376"/>
+      <c r="H25" s="376"/>
+      <c r="I25" s="376"/>
+      <c r="J25" s="376"/>
+      <c r="K25" s="376"/>
+      <c r="L25" s="376"/>
+      <c r="M25" s="376"/>
+      <c r="N25" s="376"/>
+      <c r="O25" s="376"/>
+      <c r="P25" s="376"/>
+      <c r="Q25" s="376"/>
+      <c r="R25" s="376"/>
+      <c r="S25" s="376"/>
+      <c r="T25" s="376"/>
+      <c r="U25" s="376"/>
+      <c r="V25" s="376"/>
+      <c r="W25" s="376"/>
+      <c r="X25" s="376"/>
+      <c r="Y25" s="376"/>
+      <c r="Z25" s="376"/>
+      <c r="AA25" s="376"/>
+      <c r="AB25" s="376"/>
+      <c r="AC25" s="188"/>
+      <c r="AD25" s="377">
         <v>1</v>
       </c>
-      <c r="AE25" s="307"/>
-      <c r="AF25" s="307"/>
-      <c r="AG25" s="307"/>
-      <c r="AH25" s="307"/>
-      <c r="AI25" s="307"/>
-      <c r="AJ25" s="307"/>
-      <c r="AK25" s="307"/>
-      <c r="AL25" s="307"/>
-      <c r="AM25" s="307"/>
-      <c r="AN25" s="307"/>
-      <c r="AO25" s="307"/>
-      <c r="AP25" s="307"/>
-      <c r="AQ25" s="307"/>
-      <c r="AR25" s="307"/>
-      <c r="AS25" s="307"/>
-      <c r="AT25" s="307"/>
-      <c r="AU25" s="307"/>
-      <c r="AV25" s="307"/>
-      <c r="AW25" s="307"/>
-      <c r="AX25" s="307"/>
-      <c r="AY25" s="308"/>
+      <c r="AE25" s="377"/>
+      <c r="AF25" s="377"/>
+      <c r="AG25" s="377"/>
+      <c r="AH25" s="377"/>
+      <c r="AI25" s="377"/>
+      <c r="AJ25" s="377"/>
+      <c r="AK25" s="377"/>
+      <c r="AL25" s="377"/>
+      <c r="AM25" s="377"/>
+      <c r="AN25" s="377"/>
+      <c r="AO25" s="377"/>
+      <c r="AP25" s="377"/>
+      <c r="AQ25" s="377"/>
+      <c r="AR25" s="377"/>
+      <c r="AS25" s="377"/>
+      <c r="AT25" s="377"/>
+      <c r="AU25" s="377"/>
+      <c r="AV25" s="377"/>
+      <c r="AW25" s="377"/>
+      <c r="AX25" s="377"/>
+      <c r="AY25" s="378"/>
     </row>
     <row r="26" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A26" s="305"/>
-      <c r="B26" s="306"/>
-      <c r="C26" s="306"/>
-      <c r="D26" s="306"/>
-      <c r="E26" s="306"/>
-      <c r="F26" s="306"/>
-      <c r="G26" s="306"/>
-      <c r="H26" s="306"/>
-      <c r="I26" s="306"/>
-      <c r="J26" s="306"/>
-      <c r="K26" s="306"/>
-      <c r="L26" s="306"/>
-      <c r="M26" s="306"/>
-      <c r="N26" s="306"/>
-      <c r="O26" s="306"/>
-      <c r="P26" s="306"/>
-      <c r="Q26" s="306"/>
-      <c r="R26" s="306"/>
-      <c r="S26" s="306"/>
-      <c r="T26" s="306"/>
-      <c r="U26" s="306"/>
-      <c r="V26" s="306"/>
-      <c r="W26" s="306"/>
-      <c r="X26" s="306"/>
-      <c r="Y26" s="306"/>
-      <c r="Z26" s="306"/>
-      <c r="AA26" s="306"/>
-      <c r="AB26" s="306"/>
-      <c r="AC26" s="193"/>
-      <c r="AD26" s="307"/>
-      <c r="AE26" s="307"/>
-      <c r="AF26" s="307"/>
-      <c r="AG26" s="307"/>
-      <c r="AH26" s="307"/>
-      <c r="AI26" s="307"/>
-      <c r="AJ26" s="307"/>
-      <c r="AK26" s="307"/>
-      <c r="AL26" s="307"/>
-      <c r="AM26" s="307"/>
-      <c r="AN26" s="307"/>
-      <c r="AO26" s="307"/>
-      <c r="AP26" s="307"/>
-      <c r="AQ26" s="307"/>
-      <c r="AR26" s="307"/>
-      <c r="AS26" s="307"/>
-      <c r="AT26" s="307"/>
-      <c r="AU26" s="307"/>
-      <c r="AV26" s="307"/>
-      <c r="AW26" s="307"/>
-      <c r="AX26" s="307"/>
-      <c r="AY26" s="308"/>
+      <c r="A26" s="375"/>
+      <c r="B26" s="376"/>
+      <c r="C26" s="376"/>
+      <c r="D26" s="376"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
+      <c r="G26" s="376"/>
+      <c r="H26" s="376"/>
+      <c r="I26" s="376"/>
+      <c r="J26" s="376"/>
+      <c r="K26" s="376"/>
+      <c r="L26" s="376"/>
+      <c r="M26" s="376"/>
+      <c r="N26" s="376"/>
+      <c r="O26" s="376"/>
+      <c r="P26" s="376"/>
+      <c r="Q26" s="376"/>
+      <c r="R26" s="376"/>
+      <c r="S26" s="376"/>
+      <c r="T26" s="376"/>
+      <c r="U26" s="376"/>
+      <c r="V26" s="376"/>
+      <c r="W26" s="376"/>
+      <c r="X26" s="376"/>
+      <c r="Y26" s="376"/>
+      <c r="Z26" s="376"/>
+      <c r="AA26" s="376"/>
+      <c r="AB26" s="376"/>
+      <c r="AC26" s="188"/>
+      <c r="AD26" s="377"/>
+      <c r="AE26" s="377"/>
+      <c r="AF26" s="377"/>
+      <c r="AG26" s="377"/>
+      <c r="AH26" s="377"/>
+      <c r="AI26" s="377"/>
+      <c r="AJ26" s="377"/>
+      <c r="AK26" s="377"/>
+      <c r="AL26" s="377"/>
+      <c r="AM26" s="377"/>
+      <c r="AN26" s="377"/>
+      <c r="AO26" s="377"/>
+      <c r="AP26" s="377"/>
+      <c r="AQ26" s="377"/>
+      <c r="AR26" s="377"/>
+      <c r="AS26" s="377"/>
+      <c r="AT26" s="377"/>
+      <c r="AU26" s="377"/>
+      <c r="AV26" s="377"/>
+      <c r="AW26" s="377"/>
+      <c r="AX26" s="377"/>
+      <c r="AY26" s="378"/>
     </row>
     <row r="27" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A27" s="190"/>
-      <c r="AY27" s="191"/>
+      <c r="A27" s="185"/>
+      <c r="AY27" s="186"/>
     </row>
     <row r="28" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A28" s="301" t="s">
+      <c r="A28" s="371" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
-      <c r="F28" s="302"/>
-      <c r="G28" s="302"/>
-      <c r="H28" s="302"/>
-      <c r="I28" s="302"/>
-      <c r="J28" s="302"/>
-      <c r="K28" s="302"/>
-      <c r="L28" s="302"/>
-      <c r="M28" s="302"/>
-      <c r="N28" s="302"/>
-      <c r="O28" s="302"/>
-      <c r="P28" s="302"/>
-      <c r="Q28" s="302"/>
-      <c r="R28" s="302"/>
-      <c r="S28" s="302"/>
-      <c r="T28" s="302"/>
-      <c r="U28" s="302"/>
-      <c r="V28" s="302"/>
-      <c r="W28" s="302"/>
-      <c r="X28" s="302"/>
-      <c r="Y28" s="302"/>
-      <c r="Z28" s="302"/>
-      <c r="AA28" s="302"/>
-      <c r="AB28" s="302"/>
-      <c r="AC28" s="302"/>
-      <c r="AD28" s="302"/>
-      <c r="AE28" s="302"/>
-      <c r="AF28" s="302"/>
-      <c r="AG28" s="302"/>
-      <c r="AH28" s="302"/>
-      <c r="AI28" s="302"/>
-      <c r="AJ28" s="302"/>
-      <c r="AK28" s="302"/>
-      <c r="AL28" s="302"/>
-      <c r="AM28" s="302"/>
-      <c r="AN28" s="302"/>
-      <c r="AO28" s="302"/>
-      <c r="AP28" s="302"/>
-      <c r="AQ28" s="302"/>
-      <c r="AR28" s="302"/>
-      <c r="AS28" s="302"/>
-      <c r="AT28" s="302"/>
-      <c r="AU28" s="302"/>
-      <c r="AV28" s="302"/>
-      <c r="AW28" s="302"/>
-      <c r="AX28" s="302"/>
-      <c r="AY28" s="303"/>
+      <c r="B28" s="372"/>
+      <c r="C28" s="372"/>
+      <c r="D28" s="372"/>
+      <c r="E28" s="372"/>
+      <c r="F28" s="372"/>
+      <c r="G28" s="372"/>
+      <c r="H28" s="372"/>
+      <c r="I28" s="372"/>
+      <c r="J28" s="372"/>
+      <c r="K28" s="372"/>
+      <c r="L28" s="372"/>
+      <c r="M28" s="372"/>
+      <c r="N28" s="372"/>
+      <c r="O28" s="372"/>
+      <c r="P28" s="372"/>
+      <c r="Q28" s="372"/>
+      <c r="R28" s="372"/>
+      <c r="S28" s="372"/>
+      <c r="T28" s="372"/>
+      <c r="U28" s="372"/>
+      <c r="V28" s="372"/>
+      <c r="W28" s="372"/>
+      <c r="X28" s="372"/>
+      <c r="Y28" s="372"/>
+      <c r="Z28" s="372"/>
+      <c r="AA28" s="372"/>
+      <c r="AB28" s="372"/>
+      <c r="AC28" s="372"/>
+      <c r="AD28" s="372"/>
+      <c r="AE28" s="372"/>
+      <c r="AF28" s="372"/>
+      <c r="AG28" s="372"/>
+      <c r="AH28" s="372"/>
+      <c r="AI28" s="372"/>
+      <c r="AJ28" s="372"/>
+      <c r="AK28" s="372"/>
+      <c r="AL28" s="372"/>
+      <c r="AM28" s="372"/>
+      <c r="AN28" s="372"/>
+      <c r="AO28" s="372"/>
+      <c r="AP28" s="372"/>
+      <c r="AQ28" s="372"/>
+      <c r="AR28" s="372"/>
+      <c r="AS28" s="372"/>
+      <c r="AT28" s="372"/>
+      <c r="AU28" s="372"/>
+      <c r="AV28" s="372"/>
+      <c r="AW28" s="372"/>
+      <c r="AX28" s="372"/>
+      <c r="AY28" s="373"/>
     </row>
     <row r="29" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A29" s="301"/>
-      <c r="B29" s="302"/>
-      <c r="C29" s="302"/>
-      <c r="D29" s="302"/>
-      <c r="E29" s="302"/>
-      <c r="F29" s="302"/>
-      <c r="G29" s="302"/>
-      <c r="H29" s="302"/>
-      <c r="I29" s="302"/>
-      <c r="J29" s="302"/>
-      <c r="K29" s="302"/>
-      <c r="L29" s="302"/>
-      <c r="M29" s="302"/>
-      <c r="N29" s="302"/>
-      <c r="O29" s="302"/>
-      <c r="P29" s="302"/>
-      <c r="Q29" s="302"/>
-      <c r="R29" s="302"/>
-      <c r="S29" s="302"/>
-      <c r="T29" s="302"/>
-      <c r="U29" s="302"/>
-      <c r="V29" s="302"/>
-      <c r="W29" s="302"/>
-      <c r="X29" s="302"/>
-      <c r="Y29" s="302"/>
-      <c r="Z29" s="302"/>
-      <c r="AA29" s="302"/>
-      <c r="AB29" s="302"/>
-      <c r="AC29" s="302"/>
-      <c r="AD29" s="302"/>
-      <c r="AE29" s="302"/>
-      <c r="AF29" s="302"/>
-      <c r="AG29" s="302"/>
-      <c r="AH29" s="302"/>
-      <c r="AI29" s="302"/>
-      <c r="AJ29" s="302"/>
-      <c r="AK29" s="302"/>
-      <c r="AL29" s="302"/>
-      <c r="AM29" s="302"/>
-      <c r="AN29" s="302"/>
-      <c r="AO29" s="302"/>
-      <c r="AP29" s="302"/>
-      <c r="AQ29" s="302"/>
-      <c r="AR29" s="302"/>
-      <c r="AS29" s="302"/>
-      <c r="AT29" s="302"/>
-      <c r="AU29" s="302"/>
-      <c r="AV29" s="302"/>
-      <c r="AW29" s="302"/>
-      <c r="AX29" s="302"/>
-      <c r="AY29" s="303"/>
+      <c r="A29" s="371"/>
+      <c r="B29" s="372"/>
+      <c r="C29" s="372"/>
+      <c r="D29" s="372"/>
+      <c r="E29" s="372"/>
+      <c r="F29" s="372"/>
+      <c r="G29" s="372"/>
+      <c r="H29" s="372"/>
+      <c r="I29" s="372"/>
+      <c r="J29" s="372"/>
+      <c r="K29" s="372"/>
+      <c r="L29" s="372"/>
+      <c r="M29" s="372"/>
+      <c r="N29" s="372"/>
+      <c r="O29" s="372"/>
+      <c r="P29" s="372"/>
+      <c r="Q29" s="372"/>
+      <c r="R29" s="372"/>
+      <c r="S29" s="372"/>
+      <c r="T29" s="372"/>
+      <c r="U29" s="372"/>
+      <c r="V29" s="372"/>
+      <c r="W29" s="372"/>
+      <c r="X29" s="372"/>
+      <c r="Y29" s="372"/>
+      <c r="Z29" s="372"/>
+      <c r="AA29" s="372"/>
+      <c r="AB29" s="372"/>
+      <c r="AC29" s="372"/>
+      <c r="AD29" s="372"/>
+      <c r="AE29" s="372"/>
+      <c r="AF29" s="372"/>
+      <c r="AG29" s="372"/>
+      <c r="AH29" s="372"/>
+      <c r="AI29" s="372"/>
+      <c r="AJ29" s="372"/>
+      <c r="AK29" s="372"/>
+      <c r="AL29" s="372"/>
+      <c r="AM29" s="372"/>
+      <c r="AN29" s="372"/>
+      <c r="AO29" s="372"/>
+      <c r="AP29" s="372"/>
+      <c r="AQ29" s="372"/>
+      <c r="AR29" s="372"/>
+      <c r="AS29" s="372"/>
+      <c r="AT29" s="372"/>
+      <c r="AU29" s="372"/>
+      <c r="AV29" s="372"/>
+      <c r="AW29" s="372"/>
+      <c r="AX29" s="372"/>
+      <c r="AY29" s="373"/>
     </row>
     <row r="30" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A30" s="190"/>
-      <c r="AY30" s="191"/>
+      <c r="A30" s="185"/>
+      <c r="AY30" s="186"/>
     </row>
     <row r="31" spans="1:51" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A31" s="194"/>
-      <c r="B31" s="195"/>
-      <c r="C31" s="195"/>
-      <c r="D31" s="195"/>
-      <c r="E31" s="195"/>
-      <c r="F31" s="195"/>
-      <c r="G31" s="195"/>
-      <c r="H31" s="195"/>
-      <c r="I31" s="195"/>
-      <c r="J31" s="195"/>
-      <c r="K31" s="195"/>
-      <c r="L31" s="195"/>
-      <c r="M31" s="195"/>
-      <c r="N31" s="195"/>
-      <c r="O31" s="195"/>
-      <c r="P31" s="195"/>
-      <c r="Q31" s="195"/>
-      <c r="R31" s="195"/>
-      <c r="S31" s="195"/>
-      <c r="T31" s="195"/>
-      <c r="U31" s="195"/>
-      <c r="V31" s="195"/>
-      <c r="W31" s="195"/>
-      <c r="X31" s="195"/>
-      <c r="Y31" s="195"/>
-      <c r="Z31" s="195"/>
-      <c r="AA31" s="195"/>
-      <c r="AB31" s="195"/>
-      <c r="AC31" s="195"/>
-      <c r="AD31" s="195"/>
-      <c r="AE31" s="195"/>
-      <c r="AF31" s="195"/>
-      <c r="AG31" s="195"/>
-      <c r="AH31" s="195"/>
-      <c r="AI31" s="195"/>
-      <c r="AJ31" s="195"/>
-      <c r="AK31" s="195"/>
-      <c r="AL31" s="195"/>
-      <c r="AM31" s="195"/>
-      <c r="AN31" s="195"/>
-      <c r="AO31" s="195"/>
-      <c r="AP31" s="195"/>
-      <c r="AQ31" s="195"/>
-      <c r="AR31" s="195"/>
-      <c r="AS31" s="195"/>
-      <c r="AT31" s="195"/>
-      <c r="AU31" s="195"/>
-      <c r="AV31" s="195"/>
-      <c r="AW31" s="195"/>
-      <c r="AX31" s="195"/>
-      <c r="AY31" s="196"/>
+      <c r="A31" s="189"/>
+      <c r="B31" s="190"/>
+      <c r="C31" s="190"/>
+      <c r="D31" s="190"/>
+      <c r="E31" s="190"/>
+      <c r="F31" s="190"/>
+      <c r="G31" s="190"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="190"/>
+      <c r="J31" s="190"/>
+      <c r="K31" s="190"/>
+      <c r="L31" s="190"/>
+      <c r="M31" s="190"/>
+      <c r="N31" s="190"/>
+      <c r="O31" s="190"/>
+      <c r="P31" s="190"/>
+      <c r="Q31" s="190"/>
+      <c r="R31" s="190"/>
+      <c r="S31" s="190"/>
+      <c r="T31" s="190"/>
+      <c r="U31" s="190"/>
+      <c r="V31" s="190"/>
+      <c r="W31" s="190"/>
+      <c r="X31" s="190"/>
+      <c r="Y31" s="190"/>
+      <c r="Z31" s="190"/>
+      <c r="AA31" s="190"/>
+      <c r="AB31" s="190"/>
+      <c r="AC31" s="190"/>
+      <c r="AD31" s="190"/>
+      <c r="AE31" s="190"/>
+      <c r="AF31" s="190"/>
+      <c r="AG31" s="190"/>
+      <c r="AH31" s="190"/>
+      <c r="AI31" s="190"/>
+      <c r="AJ31" s="190"/>
+      <c r="AK31" s="190"/>
+      <c r="AL31" s="190"/>
+      <c r="AM31" s="190"/>
+      <c r="AN31" s="190"/>
+      <c r="AO31" s="190"/>
+      <c r="AP31" s="190"/>
+      <c r="AQ31" s="190"/>
+      <c r="AR31" s="190"/>
+      <c r="AS31" s="190"/>
+      <c r="AT31" s="190"/>
+      <c r="AU31" s="190"/>
+      <c r="AV31" s="190"/>
+      <c r="AW31" s="190"/>
+      <c r="AX31" s="190"/>
+      <c r="AY31" s="191"/>
     </row>
     <row r="32" spans="1:51" ht="14.45" customHeight="1" thickTop="1"/>
   </sheetData>
@@ -25563,6 +25480,13 @@
     <protectedRange sqref="AZ1:XFD1048576" name="メモ欄1"/>
   </protectedRanges>
   <mergeCells count="15">
+    <mergeCell ref="A28:AY29"/>
+    <mergeCell ref="Q19:U22"/>
+    <mergeCell ref="V19:Z22"/>
+    <mergeCell ref="AA19:AE22"/>
+    <mergeCell ref="AF19:AJ22"/>
+    <mergeCell ref="A25:AB26"/>
+    <mergeCell ref="AD25:AY26"/>
     <mergeCell ref="C3:AY4"/>
     <mergeCell ref="A6:AY10"/>
     <mergeCell ref="A11:AY13"/>
@@ -25571,13 +25495,6 @@
     <mergeCell ref="V18:Z18"/>
     <mergeCell ref="AA18:AE18"/>
     <mergeCell ref="AF18:AJ18"/>
-    <mergeCell ref="A28:AY29"/>
-    <mergeCell ref="Q19:U22"/>
-    <mergeCell ref="V19:Z22"/>
-    <mergeCell ref="AA19:AE22"/>
-    <mergeCell ref="AF19:AJ22"/>
-    <mergeCell ref="A25:AB26"/>
-    <mergeCell ref="AD25:AY26"/>
   </mergeCells>
   <phoneticPr fontId="16"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -25625,8 +25542,8 @@
         <v>13</v>
       </c>
       <c r="D3" s="14"/>
-      <c r="E3" s="294" t="s">
-        <v>181</v>
+      <c r="E3" s="280" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="56.25" customHeight="1">
@@ -25730,29 +25647,29 @@
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="4.33203125" style="71" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" style="168" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" style="169" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" style="164" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" style="165" customWidth="1"/>
     <col min="5" max="6" width="60.83203125" style="71" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" style="71" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" style="170" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" style="166" customWidth="1"/>
     <col min="9" max="10" width="12.83203125" style="71" customWidth="1"/>
     <col min="11" max="11" width="10.83203125" style="71" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" style="170" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="166" customWidth="1"/>
     <col min="13" max="13" width="60.83203125" style="71" customWidth="1"/>
     <col min="14" max="16384" width="9.33203125" style="71"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="55" customFormat="1" ht="15">
-      <c r="A1" s="318" t="s">
+      <c r="A1" s="379" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="318"/>
-      <c r="C1" s="318"/>
-      <c r="D1" s="319" t="s">
+      <c r="B1" s="379"/>
+      <c r="C1" s="379"/>
+      <c r="D1" s="380" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
+      <c r="E1" s="381"/>
+      <c r="F1" s="381"/>
       <c r="G1" s="51" t="s">
         <v>4</v>
       </c>
@@ -25769,12 +25686,12 @@
       <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:13" s="55" customFormat="1" ht="15">
-      <c r="A2" s="318"/>
-      <c r="B2" s="318"/>
-      <c r="C2" s="318"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
+      <c r="A2" s="379"/>
+      <c r="B2" s="379"/>
+      <c r="C2" s="379"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
       <c r="G2" s="56">
         <f>COUNTA(C4:C1048576)</f>
         <v>22</v>
@@ -25795,11 +25712,11 @@
       <c r="L2" s="54"/>
     </row>
     <row r="3" spans="1:13" s="55" customFormat="1" ht="15">
-      <c r="A3" s="321" t="s">
+      <c r="A3" s="382" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="321"/>
-      <c r="C3" s="321"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
       <c r="D3" s="58" t="s">
         <v>46</v>
       </c>
@@ -25824,7 +25741,7 @@
       <c r="K3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="60" t="s">
+      <c r="L3" s="345" t="s">
         <v>45</v>
       </c>
       <c r="M3" s="58" t="s">
@@ -25847,7 +25764,7 @@
       <c r="I4" s="66"/>
       <c r="J4" s="68"/>
       <c r="K4" s="69"/>
-      <c r="L4" s="63"/>
+      <c r="L4" s="346"/>
       <c r="M4" s="70"/>
     </row>
     <row r="5" spans="1:13" ht="15">
@@ -25866,7 +25783,7 @@
       <c r="I5" s="79"/>
       <c r="J5" s="80"/>
       <c r="K5" s="81"/>
-      <c r="L5" s="74"/>
+      <c r="L5" s="347"/>
       <c r="M5" s="82"/>
     </row>
     <row r="6" spans="1:13" ht="15">
@@ -25875,22 +25792,24 @@
       <c r="C6" s="84">
         <v>1</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="299" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="350" t="s">
+      <c r="E6" s="299" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="350" t="s">
-        <v>192</v>
+      <c r="F6" s="299" t="s">
+        <v>188</v>
       </c>
       <c r="G6" s="86"/>
       <c r="H6" s="87"/>
       <c r="I6" s="88"/>
       <c r="J6" s="89"/>
       <c r="K6" s="90"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="92"/>
+      <c r="L6" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M6" s="91"/>
     </row>
     <row r="7" spans="1:13" ht="15">
       <c r="A7" s="72"/>
@@ -25903,13 +25822,13 @@
       </c>
       <c r="E7" s="76"/>
       <c r="F7" s="76"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="95"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="94"/>
       <c r="J7" s="76"/>
       <c r="K7" s="81"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="96"/>
+      <c r="L7" s="349"/>
+      <c r="M7" s="95"/>
     </row>
     <row r="8" spans="1:13" ht="15">
       <c r="A8" s="72"/>
@@ -25920,40 +25839,44 @@
       <c r="D8" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="96" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="98"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="96"/>
       <c r="K8" s="89"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="101"/>
+      <c r="L8" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M8" s="100"/>
     </row>
     <row r="9" spans="1:13" ht="15">
       <c r="A9" s="72"/>
       <c r="B9" s="83"/>
-      <c r="C9" s="102">
+      <c r="C9" s="101">
         <v>2</v>
       </c>
-      <c r="D9" s="103"/>
-      <c r="E9" s="104" t="s">
+      <c r="D9" s="102"/>
+      <c r="E9" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="103" t="s">
+      <c r="F9" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="109"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="277" t="s">
+        <v>196</v>
+      </c>
+      <c r="M9" s="108"/>
     </row>
     <row r="10" spans="1:13" ht="15">
       <c r="A10" s="61">
@@ -25966,12 +25889,12 @@
       </c>
       <c r="E10" s="65"/>
       <c r="F10" s="65"/>
-      <c r="G10" s="110"/>
+      <c r="G10" s="109"/>
       <c r="H10" s="67"/>
       <c r="I10" s="66"/>
       <c r="J10" s="68"/>
       <c r="K10" s="69"/>
-      <c r="L10" s="111"/>
+      <c r="L10" s="350"/>
       <c r="M10" s="70"/>
     </row>
     <row r="11" spans="1:13" ht="15">
@@ -25990,29 +25913,31 @@
       <c r="I11" s="79"/>
       <c r="J11" s="80"/>
       <c r="K11" s="81"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="112"/>
+      <c r="L11" s="349"/>
+      <c r="M11" s="111"/>
     </row>
     <row r="12" spans="1:13" ht="15">
       <c r="A12" s="72"/>
       <c r="B12" s="83"/>
-      <c r="C12" s="113">
+      <c r="C12" s="112">
         <v>1</v>
       </c>
-      <c r="D12" s="114" t="s">
+      <c r="D12" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115" t="s">
+      <c r="E12" s="114"/>
+      <c r="F12" s="114" t="s">
         <v>128</v>
       </c>
       <c r="G12" s="86"/>
       <c r="H12" s="87"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="119"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="351" t="s">
+        <v>195</v>
+      </c>
+      <c r="M12" s="117"/>
     </row>
     <row r="13" spans="1:13" ht="15">
       <c r="A13" s="72"/>
@@ -26030,8 +25955,8 @@
       <c r="I13" s="79"/>
       <c r="J13" s="80"/>
       <c r="K13" s="81"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="112"/>
+      <c r="L13" s="349"/>
+      <c r="M13" s="111"/>
     </row>
     <row r="14" spans="1:13" ht="30">
       <c r="A14" s="72"/>
@@ -26042,40 +25967,44 @@
       <c r="D14" s="85" t="s">
         <v>129</v>
       </c>
-      <c r="E14" s="97" t="s">
+      <c r="E14" s="96" t="s">
         <v>74</v>
       </c>
       <c r="F14" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="98"/>
-      <c r="H14" s="99"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="98"/>
       <c r="I14" s="88"/>
       <c r="J14" s="89"/>
       <c r="K14" s="89"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="92"/>
+      <c r="L14" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M14" s="91"/>
     </row>
     <row r="15" spans="1:13" ht="15">
       <c r="A15" s="72"/>
       <c r="B15" s="83"/>
-      <c r="C15" s="102">
+      <c r="C15" s="101">
         <v>2</v>
       </c>
-      <c r="D15" s="103"/>
-      <c r="E15" s="104" t="s">
+      <c r="D15" s="102"/>
+      <c r="E15" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="104" t="s">
+      <c r="F15" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="105"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="108"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="121"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="277" t="s">
+        <v>196</v>
+      </c>
+      <c r="M15" s="119"/>
     </row>
     <row r="16" spans="1:13" ht="15">
       <c r="A16" s="61">
@@ -26088,16 +26017,16 @@
       </c>
       <c r="E16" s="65"/>
       <c r="F16" s="65"/>
-      <c r="G16" s="110"/>
+      <c r="G16" s="109"/>
       <c r="H16" s="67"/>
       <c r="I16" s="66"/>
       <c r="J16" s="68"/>
       <c r="K16" s="69"/>
-      <c r="L16" s="111"/>
+      <c r="L16" s="350"/>
       <c r="M16" s="70"/>
     </row>
     <row r="17" spans="1:13" ht="15">
-      <c r="A17" s="122"/>
+      <c r="A17" s="120"/>
       <c r="B17" s="73">
         <v>1</v>
       </c>
@@ -26112,29 +26041,31 @@
       <c r="I17" s="79"/>
       <c r="J17" s="80"/>
       <c r="K17" s="81"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="112"/>
+      <c r="L17" s="349"/>
+      <c r="M17" s="111"/>
     </row>
     <row r="18" spans="1:13" ht="15">
-      <c r="A18" s="122"/>
+      <c r="A18" s="120"/>
       <c r="B18" s="83"/>
-      <c r="C18" s="113">
+      <c r="C18" s="112">
         <v>1</v>
       </c>
-      <c r="D18" s="114" t="s">
+      <c r="D18" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115" t="s">
+      <c r="E18" s="114"/>
+      <c r="F18" s="114" t="s">
         <v>131</v>
       </c>
       <c r="G18" s="86"/>
       <c r="H18" s="87"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="119"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="351" t="s">
+        <v>195</v>
+      </c>
+      <c r="M18" s="117"/>
     </row>
     <row r="19" spans="1:13" ht="15">
       <c r="A19" s="72"/>
@@ -26147,13 +26078,13 @@
       </c>
       <c r="E19" s="81"/>
       <c r="F19" s="76"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="95"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="94"/>
       <c r="J19" s="76"/>
       <c r="K19" s="81"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="96"/>
+      <c r="L19" s="349"/>
+      <c r="M19" s="95"/>
     </row>
     <row r="20" spans="1:13" ht="105">
       <c r="A20" s="72"/>
@@ -26162,66 +26093,72 @@
         <v>1</v>
       </c>
       <c r="D20" s="85"/>
-      <c r="E20" s="97" t="s">
+      <c r="E20" s="96" t="s">
         <v>147</v>
       </c>
       <c r="F20" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="98"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="96"/>
       <c r="K20" s="89"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="287" t="s">
-        <v>177</v>
+      <c r="L20" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M20" s="273" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="106.5" customHeight="1">
       <c r="A21" s="72"/>
       <c r="B21" s="83"/>
-      <c r="C21" s="123">
+      <c r="C21" s="121">
         <v>2</v>
       </c>
-      <c r="D21" s="124"/>
-      <c r="E21" s="124" t="s">
+      <c r="D21" s="122"/>
+      <c r="E21" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="125" t="s">
+      <c r="F21" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="G21" s="181"/>
-      <c r="H21" s="182"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="287" t="s">
-        <v>178</v>
+      <c r="G21" s="177"/>
+      <c r="H21" s="178"/>
+      <c r="I21" s="124"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="352" t="s">
+        <v>195</v>
+      </c>
+      <c r="M21" s="273" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="45">
-      <c r="A22" s="176"/>
-      <c r="B22" s="180"/>
-      <c r="C22" s="102">
+      <c r="A22" s="172"/>
+      <c r="B22" s="176"/>
+      <c r="C22" s="101">
         <v>3</v>
       </c>
-      <c r="D22" s="177"/>
-      <c r="E22" s="177" t="s">
+      <c r="D22" s="173"/>
+      <c r="E22" s="173" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="177" t="s">
+      <c r="F22" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="178"/>
-      <c r="J22" s="179"/>
-      <c r="K22" s="149"/>
-      <c r="L22" s="129"/>
-      <c r="M22" s="288" t="s">
-        <v>175</v>
+      <c r="G22" s="104"/>
+      <c r="H22" s="179"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="146"/>
+      <c r="L22" s="353" t="s">
+        <v>196</v>
+      </c>
+      <c r="M22" s="274" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15">
@@ -26235,37 +26172,37 @@
       </c>
       <c r="E23" s="65"/>
       <c r="F23" s="65"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="132"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="129"/>
       <c r="J23" s="65"/>
       <c r="K23" s="69"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="133"/>
+      <c r="L23" s="350"/>
+      <c r="M23" s="130"/>
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A24" s="16"/>
       <c r="B24" s="43">
         <v>1</v>
       </c>
-      <c r="C24" s="134"/>
-      <c r="D24" s="135" t="s">
+      <c r="C24" s="131"/>
+      <c r="D24" s="132" t="s">
         <v>55</v>
       </c>
       <c r="E24" s="44"/>
-      <c r="F24" s="136"/>
-      <c r="G24" s="137"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="136"/>
-      <c r="K24" s="140"/>
-      <c r="L24" s="141"/>
-      <c r="M24" s="142"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="137"/>
+      <c r="L24" s="354"/>
+      <c r="M24" s="139"/>
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A25" s="16"/>
       <c r="B25" s="17"/>
-      <c r="C25" s="143">
+      <c r="C25" s="140">
         <v>1</v>
       </c>
       <c r="D25" s="45" t="s">
@@ -26274,16 +26211,18 @@
       <c r="E25" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="144" t="s">
+      <c r="F25" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="98"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="145"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="142"/>
       <c r="J25" s="46"/>
-      <c r="K25" s="146"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="101"/>
+      <c r="K25" s="143"/>
+      <c r="L25" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M25" s="100"/>
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A26" s="16"/>
@@ -26298,37 +26237,39 @@
       <c r="F26" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="147"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="148"/>
+      <c r="G26" s="144"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="145"/>
       <c r="J26" s="33"/>
-      <c r="K26" s="149"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="109"/>
+      <c r="K26" s="146"/>
+      <c r="L26" s="355" t="s">
+        <v>195</v>
+      </c>
+      <c r="M26" s="108"/>
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A27" s="16"/>
       <c r="B27" s="43">
         <v>2</v>
       </c>
-      <c r="C27" s="134"/>
-      <c r="D27" s="135" t="s">
+      <c r="C27" s="131"/>
+      <c r="D27" s="132" t="s">
         <v>53</v>
       </c>
       <c r="E27" s="44"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="138"/>
-      <c r="I27" s="139"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="140"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="142"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="134"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="137"/>
+      <c r="L27" s="354"/>
+      <c r="M27" s="139"/>
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" ht="75">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
-      <c r="C28" s="143">
+      <c r="C28" s="140">
         <v>1</v>
       </c>
       <c r="D28" s="46" t="s">
@@ -26337,16 +26278,18 @@
       <c r="E28" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="144" t="s">
+      <c r="F28" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="G28" s="98"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="145"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="98"/>
+      <c r="I28" s="142"/>
       <c r="J28" s="46"/>
-      <c r="K28" s="146"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="101"/>
+      <c r="K28" s="143"/>
+      <c r="L28" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M28" s="100"/>
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A29" s="16"/>
@@ -26361,13 +26304,15 @@
       <c r="F29" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="150"/>
+      <c r="G29" s="147"/>
       <c r="H29" s="36"/>
-      <c r="I29" s="151"/>
+      <c r="I29" s="148"/>
       <c r="J29" s="37"/>
-      <c r="K29" s="152"/>
-      <c r="L29" s="153"/>
-      <c r="M29" s="130"/>
+      <c r="K29" s="149"/>
+      <c r="L29" s="352" t="s">
+        <v>195</v>
+      </c>
+      <c r="M29" s="127"/>
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A30" s="16"/>
@@ -26382,13 +26327,15 @@
       <c r="F30" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G30" s="147"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="148"/>
+      <c r="G30" s="144"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="145"/>
       <c r="J30" s="33"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="129"/>
-      <c r="M30" s="109"/>
+      <c r="K30" s="146"/>
+      <c r="L30" s="355" t="s">
+        <v>195</v>
+      </c>
+      <c r="M30" s="108"/>
     </row>
     <row r="31" spans="1:13" ht="15">
       <c r="A31" s="61">
@@ -26401,137 +26348,141 @@
       </c>
       <c r="E31" s="65"/>
       <c r="F31" s="65"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="132"/>
+      <c r="G31" s="128"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="129"/>
       <c r="J31" s="65"/>
       <c r="K31" s="69"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="133"/>
+      <c r="L31" s="350"/>
+      <c r="M31" s="130"/>
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A32" s="16"/>
       <c r="B32" s="43">
         <v>1</v>
       </c>
-      <c r="C32" s="134"/>
+      <c r="C32" s="131"/>
       <c r="D32" s="75" t="s">
         <v>125</v>
       </c>
       <c r="E32" s="44"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="138"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="136"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="141"/>
-      <c r="M32" s="142"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="137"/>
+      <c r="L32" s="354"/>
+      <c r="M32" s="139"/>
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" ht="30">
       <c r="A33" s="16"/>
       <c r="B33" s="17"/>
-      <c r="C33" s="143">
+      <c r="C33" s="140">
         <v>1</v>
       </c>
-      <c r="D33" s="114" t="s">
+      <c r="D33" s="113" t="s">
         <v>150</v>
       </c>
       <c r="E33" s="45"/>
-      <c r="F33" s="144" t="s">
+      <c r="F33" s="141" t="s">
         <v>134</v>
       </c>
       <c r="G33" s="86"/>
       <c r="H33" s="87"/>
-      <c r="I33" s="145"/>
+      <c r="I33" s="142"/>
       <c r="J33" s="46"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="101"/>
+      <c r="K33" s="143"/>
+      <c r="L33" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M33" s="100"/>
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A34" s="16"/>
       <c r="B34" s="43">
         <v>2</v>
       </c>
-      <c r="C34" s="154"/>
+      <c r="C34" s="150"/>
       <c r="D34" s="48" t="s">
         <v>122</v>
       </c>
       <c r="E34" s="49"/>
       <c r="F34" s="50"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="155"/>
-      <c r="J34" s="157"/>
-      <c r="K34" s="158"/>
-      <c r="L34" s="158"/>
-      <c r="M34" s="159"/>
+      <c r="G34" s="151"/>
+      <c r="H34" s="152"/>
+      <c r="I34" s="151"/>
+      <c r="J34" s="153"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="356"/>
+      <c r="M34" s="155"/>
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" ht="120">
       <c r="A35" s="16"/>
       <c r="B35" s="47"/>
-      <c r="C35" s="387">
+      <c r="C35" s="335">
         <v>1</v>
       </c>
-      <c r="D35" s="388" t="s">
+      <c r="D35" s="336" t="s">
         <v>123</v>
       </c>
-      <c r="E35" s="389" t="s">
+      <c r="E35" s="337" t="s">
         <v>154</v>
       </c>
-      <c r="F35" s="389" t="s">
+      <c r="F35" s="337" t="s">
         <v>86</v>
       </c>
-      <c r="G35" s="390"/>
-      <c r="H35" s="391"/>
-      <c r="I35" s="390"/>
-      <c r="J35" s="392"/>
-      <c r="K35" s="393"/>
-      <c r="L35" s="394"/>
-      <c r="M35" s="395" t="s">
-        <v>176</v>
-      </c>
+      <c r="G35" s="338"/>
+      <c r="H35" s="339"/>
+      <c r="I35" s="338"/>
+      <c r="J35" s="340"/>
+      <c r="K35" s="341"/>
+      <c r="L35" s="357" t="s">
+        <v>195</v>
+      </c>
+      <c r="M35" s="342"/>
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A36" s="16"/>
       <c r="B36" s="43">
         <v>3</v>
       </c>
-      <c r="C36" s="134"/>
+      <c r="C36" s="131"/>
       <c r="D36" s="75" t="s">
         <v>135</v>
       </c>
       <c r="E36" s="76"/>
       <c r="F36" s="76"/>
-      <c r="G36" s="137"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="139"/>
-      <c r="J36" s="136"/>
-      <c r="K36" s="140"/>
-      <c r="L36" s="141"/>
-      <c r="M36" s="142"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="133"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="354"/>
+      <c r="M36" s="139"/>
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" ht="75">
       <c r="A37" s="16"/>
       <c r="B37" s="17"/>
-      <c r="C37" s="143">
+      <c r="C37" s="140">
         <v>1</v>
       </c>
-      <c r="D37" s="114" t="s">
+      <c r="D37" s="113" t="s">
         <v>136</v>
       </c>
-      <c r="E37" s="115"/>
-      <c r="F37" s="114" t="s">
+      <c r="E37" s="114"/>
+      <c r="F37" s="113" t="s">
         <v>137</v>
       </c>
       <c r="G37" s="86"/>
       <c r="H37" s="87"/>
-      <c r="I37" s="145"/>
+      <c r="I37" s="142"/>
       <c r="J37" s="46"/>
-      <c r="K37" s="146"/>
-      <c r="L37" s="91"/>
-      <c r="M37" s="101"/>
+      <c r="K37" s="143"/>
+      <c r="L37" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M37" s="100"/>
     </row>
     <row r="38" spans="1:13" ht="15">
       <c r="A38" s="72"/>
@@ -26544,34 +26495,36 @@
       </c>
       <c r="E38" s="76"/>
       <c r="F38" s="76"/>
-      <c r="G38" s="93"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="95"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="94"/>
       <c r="J38" s="76"/>
       <c r="K38" s="81"/>
-      <c r="L38" s="94"/>
-      <c r="M38" s="96"/>
+      <c r="L38" s="349"/>
+      <c r="M38" s="95"/>
     </row>
     <row r="39" spans="1:13" ht="45">
-      <c r="A39" s="161"/>
-      <c r="B39" s="162"/>
-      <c r="C39" s="113">
+      <c r="A39" s="157"/>
+      <c r="B39" s="158"/>
+      <c r="C39" s="112">
         <v>1</v>
       </c>
-      <c r="D39" s="114" t="s">
+      <c r="D39" s="113" t="s">
         <v>138</v>
       </c>
-      <c r="E39" s="115"/>
-      <c r="F39" s="114" t="s">
+      <c r="E39" s="114"/>
+      <c r="F39" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="G39" s="163"/>
-      <c r="H39" s="164"/>
-      <c r="I39" s="165"/>
-      <c r="J39" s="115"/>
-      <c r="K39" s="166"/>
-      <c r="L39" s="118"/>
-      <c r="M39" s="167"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="160"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="114"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="351" t="s">
+        <v>195</v>
+      </c>
+      <c r="M39" s="163"/>
     </row>
     <row r="40" spans="1:13" ht="15">
       <c r="A40" s="61">
@@ -26584,53 +26537,55 @@
       </c>
       <c r="E40" s="65"/>
       <c r="F40" s="65"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="111"/>
-      <c r="I40" s="132"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="110"/>
+      <c r="I40" s="129"/>
       <c r="J40" s="65"/>
       <c r="K40" s="69"/>
-      <c r="L40" s="111"/>
-      <c r="M40" s="133"/>
+      <c r="L40" s="350"/>
+      <c r="M40" s="130"/>
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A41" s="16"/>
       <c r="B41" s="43">
         <v>1</v>
       </c>
-      <c r="C41" s="134"/>
+      <c r="C41" s="131"/>
       <c r="D41" s="75" t="s">
         <v>139</v>
       </c>
       <c r="E41" s="76"/>
       <c r="F41" s="76"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="139"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="140"/>
-      <c r="L41" s="141"/>
-      <c r="M41" s="142"/>
+      <c r="G41" s="134"/>
+      <c r="H41" s="135"/>
+      <c r="I41" s="136"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="137"/>
+      <c r="L41" s="354"/>
+      <c r="M41" s="139"/>
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" ht="15">
       <c r="A42" s="16"/>
       <c r="B42" s="17"/>
-      <c r="C42" s="143">
+      <c r="C42" s="140">
         <v>1</v>
       </c>
-      <c r="D42" s="114" t="s">
+      <c r="D42" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="E42" s="115"/>
-      <c r="F42" s="115" t="s">
+      <c r="E42" s="114"/>
+      <c r="F42" s="114" t="s">
         <v>141</v>
       </c>
       <c r="G42" s="86"/>
       <c r="H42" s="87"/>
-      <c r="I42" s="145"/>
+      <c r="I42" s="142"/>
       <c r="J42" s="46"/>
-      <c r="K42" s="146"/>
-      <c r="L42" s="91"/>
-      <c r="M42" s="101"/>
+      <c r="K42" s="143"/>
+      <c r="L42" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M42" s="100"/>
     </row>
     <row r="43" spans="1:13" ht="15">
       <c r="A43" s="61">
@@ -26643,13 +26598,13 @@
       </c>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
-      <c r="G43" s="131"/>
-      <c r="H43" s="111"/>
-      <c r="I43" s="132"/>
+      <c r="G43" s="128"/>
+      <c r="H43" s="110"/>
+      <c r="I43" s="129"/>
       <c r="J43" s="65"/>
       <c r="K43" s="69"/>
-      <c r="L43" s="111"/>
-      <c r="M43" s="133"/>
+      <c r="L43" s="350"/>
+      <c r="M43" s="130"/>
     </row>
     <row r="44" spans="1:13" ht="15">
       <c r="A44" s="72"/>
@@ -26662,13 +26617,13 @@
       </c>
       <c r="E44" s="76"/>
       <c r="F44" s="76"/>
-      <c r="G44" s="93"/>
-      <c r="H44" s="94"/>
-      <c r="I44" s="95"/>
+      <c r="G44" s="92"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="94"/>
       <c r="J44" s="76"/>
       <c r="K44" s="81"/>
-      <c r="L44" s="94"/>
-      <c r="M44" s="96"/>
+      <c r="L44" s="349"/>
+      <c r="M44" s="95"/>
     </row>
     <row r="45" spans="1:13" ht="30">
       <c r="A45" s="72"/>
@@ -26679,40 +26634,44 @@
       <c r="D45" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="97" t="s">
+      <c r="E45" s="96" t="s">
         <v>69</v>
       </c>
       <c r="F45" s="85" t="s">
         <v>152</v>
       </c>
-      <c r="G45" s="98"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="100"/>
-      <c r="J45" s="97"/>
+      <c r="G45" s="97"/>
+      <c r="H45" s="98"/>
+      <c r="I45" s="99"/>
+      <c r="J45" s="96"/>
       <c r="K45" s="90"/>
-      <c r="L45" s="91"/>
-      <c r="M45" s="101"/>
+      <c r="L45" s="348" t="s">
+        <v>195</v>
+      </c>
+      <c r="M45" s="100"/>
     </row>
     <row r="46" spans="1:13" ht="30">
-      <c r="A46" s="161"/>
-      <c r="B46" s="162"/>
-      <c r="C46" s="102">
+      <c r="A46" s="157"/>
+      <c r="B46" s="158"/>
+      <c r="C46" s="101">
         <v>2</v>
       </c>
-      <c r="D46" s="103"/>
-      <c r="E46" s="104" t="s">
+      <c r="D46" s="102"/>
+      <c r="E46" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="103" t="s">
+      <c r="F46" s="102" t="s">
         <v>153</v>
       </c>
-      <c r="G46" s="105"/>
-      <c r="H46" s="106"/>
-      <c r="I46" s="107"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="149"/>
-      <c r="L46" s="129"/>
-      <c r="M46" s="109"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="106"/>
+      <c r="J46" s="103"/>
+      <c r="K46" s="146"/>
+      <c r="L46" s="355" t="s">
+        <v>195</v>
+      </c>
+      <c r="M46" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -26723,7 +26682,6 @@
   <phoneticPr fontId="16"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -26750,16 +26708,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="322" t="s">
+      <c r="A1" s="383" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="322"/>
-      <c r="C1" s="322"/>
-      <c r="D1" s="324" t="s">
+      <c r="B1" s="383"/>
+      <c r="C1" s="383"/>
+      <c r="D1" s="385" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
+      <c r="E1" s="385"/>
+      <c r="F1" s="385"/>
       <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
@@ -26776,12 +26734,12 @@
       <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="322"/>
-      <c r="B2" s="322"/>
-      <c r="C2" s="322"/>
-      <c r="D2" s="325"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="325"/>
+      <c r="A2" s="383"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="386"/>
+      <c r="E2" s="386"/>
+      <c r="F2" s="386"/>
       <c r="G2" s="5">
         <f>COUNTA(C4:C1048576)</f>
         <v>12</v>
@@ -26802,11 +26760,11 @@
       <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="323" t="s">
+      <c r="A3" s="384" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="323"/>
-      <c r="C3" s="323"/>
+      <c r="B3" s="384"/>
+      <c r="C3" s="384"/>
       <c r="D3" s="18" t="s">
         <v>46</v>
       </c>
@@ -26825,7 +26783,7 @@
       <c r="I3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="171" t="s">
+      <c r="J3" s="167" t="s">
         <v>142</v>
       </c>
       <c r="K3" s="21" t="s">
@@ -26839,41 +26797,41 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="351">
+      <c r="A4" s="300">
         <v>1</v>
       </c>
-      <c r="B4" s="352"/>
-      <c r="C4" s="353"/>
-      <c r="D4" s="354" t="s">
+      <c r="B4" s="301"/>
+      <c r="C4" s="302"/>
+      <c r="D4" s="303" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="355"/>
-      <c r="F4" s="355"/>
-      <c r="G4" s="356"/>
-      <c r="H4" s="357"/>
-      <c r="I4" s="356"/>
-      <c r="J4" s="358"/>
-      <c r="K4" s="355"/>
-      <c r="L4" s="355"/>
+      <c r="E4" s="304"/>
+      <c r="F4" s="304"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="306"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="307"/>
+      <c r="K4" s="304"/>
+      <c r="L4" s="304"/>
       <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="16"/>
-      <c r="B5" s="359">
+      <c r="B5" s="308">
         <v>1</v>
       </c>
-      <c r="C5" s="289"/>
+      <c r="C5" s="275"/>
       <c r="D5" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="360"/>
-      <c r="G5" s="141"/>
-      <c r="H5" s="361"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="362"/>
-      <c r="K5" s="360"/>
-      <c r="L5" s="360"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="309"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="310"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="309"/>
+      <c r="L5" s="343"/>
       <c r="M5" s="27"/>
     </row>
     <row r="6" spans="1:13" ht="45">
@@ -26889,33 +26847,35 @@
         <v>84</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="363"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="145"/>
-      <c r="J6" s="365"/>
-      <c r="K6" s="366"/>
-      <c r="L6" s="367"/>
+        <v>189</v>
+      </c>
+      <c r="G6" s="312"/>
+      <c r="H6" s="313"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="314"/>
+      <c r="K6" s="315"/>
+      <c r="L6" s="344" t="s">
+        <v>195</v>
+      </c>
       <c r="M6" s="40"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="16"/>
-      <c r="B7" s="359">
+      <c r="B7" s="308">
         <v>2</v>
       </c>
-      <c r="C7" s="289"/>
+      <c r="C7" s="275"/>
       <c r="D7" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="368"/>
-      <c r="F7" s="369"/>
-      <c r="G7" s="370"/>
-      <c r="H7" s="371"/>
-      <c r="I7" s="370"/>
-      <c r="J7" s="371"/>
-      <c r="K7" s="372"/>
-      <c r="L7" s="371"/>
+      <c r="E7" s="316"/>
+      <c r="F7" s="317"/>
+      <c r="G7" s="318"/>
+      <c r="H7" s="319"/>
+      <c r="I7" s="318"/>
+      <c r="J7" s="319"/>
+      <c r="K7" s="320"/>
+      <c r="L7" s="319"/>
       <c r="M7" s="27"/>
     </row>
     <row r="8" spans="1:13">
@@ -26928,55 +26888,57 @@
         <v>67</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F8" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="G8" s="363"/>
-      <c r="H8" s="364"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="365"/>
-      <c r="K8" s="366"/>
-      <c r="L8" s="367"/>
-      <c r="M8" s="184"/>
+      <c r="G8" s="312"/>
+      <c r="H8" s="313"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="314"/>
+      <c r="K8" s="315"/>
+      <c r="L8" s="344" t="s">
+        <v>195</v>
+      </c>
+      <c r="M8" s="180"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="351">
+      <c r="A9" s="300">
         <v>2</v>
       </c>
-      <c r="B9" s="352"/>
-      <c r="C9" s="353"/>
-      <c r="D9" s="354" t="s">
+      <c r="B9" s="301"/>
+      <c r="C9" s="302"/>
+      <c r="D9" s="303" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="373"/>
-      <c r="F9" s="374"/>
-      <c r="G9" s="375"/>
-      <c r="H9" s="376"/>
-      <c r="I9" s="375"/>
-      <c r="J9" s="376"/>
-      <c r="K9" s="377"/>
-      <c r="L9" s="376"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="323"/>
+      <c r="H9" s="324"/>
+      <c r="I9" s="323"/>
+      <c r="J9" s="324"/>
+      <c r="K9" s="325"/>
+      <c r="L9" s="324"/>
       <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="16"/>
-      <c r="B10" s="359">
+      <c r="B10" s="308">
         <v>1</v>
       </c>
-      <c r="C10" s="289"/>
+      <c r="C10" s="275"/>
       <c r="D10" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="368"/>
-      <c r="F10" s="369"/>
-      <c r="G10" s="370"/>
-      <c r="H10" s="371"/>
-      <c r="I10" s="370"/>
-      <c r="J10" s="371"/>
-      <c r="K10" s="372"/>
-      <c r="L10" s="371"/>
+      <c r="E10" s="316"/>
+      <c r="F10" s="317"/>
+      <c r="G10" s="318"/>
+      <c r="H10" s="319"/>
+      <c r="I10" s="318"/>
+      <c r="J10" s="319"/>
+      <c r="K10" s="320"/>
+      <c r="L10" s="319"/>
       <c r="M10" s="27"/>
     </row>
     <row r="11" spans="1:13" ht="30">
@@ -26992,14 +26954,16 @@
         <v>33</v>
       </c>
       <c r="F11" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="272"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="314"/>
+      <c r="K11" s="315"/>
+      <c r="L11" s="344" t="s">
         <v>195</v>
       </c>
-      <c r="G11" s="286"/>
-      <c r="H11" s="285"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="365"/>
-      <c r="K11" s="366"/>
-      <c r="L11" s="367"/>
       <c r="M11" s="40"/>
     </row>
     <row r="12" spans="1:13">
@@ -27013,14 +26977,16 @@
         <v>19</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="G12" s="286"/>
-      <c r="H12" s="285"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="378"/>
-      <c r="K12" s="160"/>
-      <c r="L12" s="172"/>
+        <v>192</v>
+      </c>
+      <c r="G12" s="272"/>
+      <c r="H12" s="271"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="326"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="168" t="s">
+        <v>195</v>
+      </c>
       <c r="M12" s="42"/>
     </row>
     <row r="13" spans="1:13">
@@ -27034,14 +27000,16 @@
         <v>20</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" s="286"/>
-      <c r="H13" s="285"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="378"/>
-      <c r="K13" s="160"/>
-      <c r="L13" s="172"/>
+        <v>193</v>
+      </c>
+      <c r="G13" s="272"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="148"/>
+      <c r="J13" s="326"/>
+      <c r="K13" s="156"/>
+      <c r="L13" s="168" t="s">
+        <v>195</v>
+      </c>
       <c r="M13" s="42"/>
     </row>
     <row r="14" spans="1:13">
@@ -27057,12 +27025,14 @@
       <c r="F14" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="286"/>
-      <c r="H14" s="285"/>
-      <c r="I14" s="151"/>
-      <c r="J14" s="378"/>
-      <c r="K14" s="160"/>
-      <c r="L14" s="172"/>
+      <c r="G14" s="272"/>
+      <c r="H14" s="271"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="326"/>
+      <c r="K14" s="156"/>
+      <c r="L14" s="168" t="s">
+        <v>195</v>
+      </c>
       <c r="M14" s="42"/>
     </row>
     <row r="15" spans="1:13">
@@ -27078,31 +27048,33 @@
       <c r="F15" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="148"/>
-      <c r="H15" s="290"/>
-      <c r="I15" s="148"/>
-      <c r="J15" s="379"/>
-      <c r="K15" s="174"/>
-      <c r="L15" s="173"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="276"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="327"/>
+      <c r="K15" s="170"/>
+      <c r="L15" s="169" t="s">
+        <v>195</v>
+      </c>
       <c r="M15" s="41"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="16"/>
-      <c r="B16" s="359">
+      <c r="B16" s="308">
         <v>2</v>
       </c>
-      <c r="C16" s="289"/>
+      <c r="C16" s="275"/>
       <c r="D16" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="136"/>
-      <c r="F16" s="380"/>
-      <c r="G16" s="381"/>
-      <c r="H16" s="382"/>
-      <c r="I16" s="381"/>
-      <c r="J16" s="383"/>
-      <c r="K16" s="384"/>
-      <c r="L16" s="382"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="328"/>
+      <c r="G16" s="329"/>
+      <c r="H16" s="330"/>
+      <c r="I16" s="329"/>
+      <c r="J16" s="331"/>
+      <c r="K16" s="332"/>
+      <c r="L16" s="330"/>
       <c r="M16" s="27"/>
     </row>
     <row r="17" spans="1:13" ht="30">
@@ -27118,14 +27090,16 @@
         <v>33</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="G17" s="286"/>
-      <c r="H17" s="285"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="385"/>
-      <c r="K17" s="366"/>
-      <c r="L17" s="367"/>
+        <v>194</v>
+      </c>
+      <c r="G17" s="272"/>
+      <c r="H17" s="271"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="333"/>
+      <c r="K17" s="315"/>
+      <c r="L17" s="344" t="s">
+        <v>195</v>
+      </c>
       <c r="M17" s="40"/>
     </row>
     <row r="18" spans="1:13">
@@ -27141,12 +27115,14 @@
       <c r="F18" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="286"/>
-      <c r="H18" s="285"/>
-      <c r="I18" s="151"/>
-      <c r="J18" s="386"/>
-      <c r="K18" s="160"/>
-      <c r="L18" s="172"/>
+      <c r="G18" s="272"/>
+      <c r="H18" s="271"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="334"/>
+      <c r="K18" s="156"/>
+      <c r="L18" s="168" t="s">
+        <v>195</v>
+      </c>
       <c r="M18" s="42"/>
     </row>
     <row r="19" spans="1:13">
@@ -27162,12 +27138,14 @@
       <c r="F19" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="286"/>
-      <c r="H19" s="285"/>
-      <c r="I19" s="151"/>
-      <c r="J19" s="378"/>
-      <c r="K19" s="160"/>
-      <c r="L19" s="172"/>
+      <c r="G19" s="272"/>
+      <c r="H19" s="271"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="326"/>
+      <c r="K19" s="156"/>
+      <c r="L19" s="168" t="s">
+        <v>195</v>
+      </c>
       <c r="M19" s="42"/>
     </row>
     <row r="20" spans="1:13">
@@ -27183,12 +27161,14 @@
       <c r="F20" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="286"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="151"/>
-      <c r="J20" s="378"/>
-      <c r="K20" s="160"/>
-      <c r="L20" s="172"/>
+      <c r="G20" s="272"/>
+      <c r="H20" s="271"/>
+      <c r="I20" s="148"/>
+      <c r="J20" s="326"/>
+      <c r="K20" s="156"/>
+      <c r="L20" s="168" t="s">
+        <v>195</v>
+      </c>
       <c r="M20" s="42"/>
     </row>
     <row r="21" spans="1:13">
@@ -27204,12 +27184,14 @@
       <c r="F21" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="148"/>
-      <c r="H21" s="290"/>
-      <c r="I21" s="148"/>
-      <c r="J21" s="291"/>
-      <c r="K21" s="174"/>
-      <c r="L21" s="173"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="276"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="277"/>
+      <c r="K21" s="170"/>
+      <c r="L21" s="169" t="s">
+        <v>195</v>
+      </c>
       <c r="M21" s="41"/>
     </row>
   </sheetData>
@@ -27232,855 +27214,847 @@
   <dimension ref="A1:O87"/>
   <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="222" customWidth="1"/>
-    <col min="2" max="3" width="5.6640625" style="222" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="223" customWidth="1"/>
-    <col min="5" max="5" width="43.1640625" style="222" customWidth="1"/>
-    <col min="6" max="6" width="75.33203125" style="222" customWidth="1"/>
-    <col min="7" max="7" width="72.6640625" style="222" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" style="222" customWidth="1"/>
-    <col min="9" max="9" width="99.83203125" style="222" customWidth="1"/>
-    <col min="10" max="11" width="13.5" style="222" customWidth="1"/>
-    <col min="12" max="13" width="18.33203125" style="223" customWidth="1"/>
-    <col min="14" max="15" width="18.33203125" style="222" customWidth="1"/>
-    <col min="16" max="16384" width="13.5" style="222"/>
+    <col min="1" max="1" width="4.33203125" style="215" customWidth="1"/>
+    <col min="2" max="3" width="5.6640625" style="215" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="216" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" style="215" customWidth="1"/>
+    <col min="6" max="6" width="75.33203125" style="215" customWidth="1"/>
+    <col min="7" max="7" width="72.6640625" style="215" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="215" customWidth="1"/>
+    <col min="9" max="9" width="99.83203125" style="215" customWidth="1"/>
+    <col min="10" max="11" width="13.5" style="215" customWidth="1"/>
+    <col min="12" max="13" width="18.33203125" style="216" customWidth="1"/>
+    <col min="14" max="15" width="18.33203125" style="215" customWidth="1"/>
+    <col min="16" max="16384" width="13.5" style="215"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1">
       <c r="I1"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="326" t="s">
+      <c r="B2" s="387" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="327"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="327"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="280" t="s">
+      <c r="C2" s="388"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
+      <c r="F2" s="389"/>
+      <c r="G2" s="267" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="217"/>
+      <c r="H2" s="211"/>
       <c r="I2"/>
     </row>
     <row r="3" spans="1:15" ht="16.5">
-      <c r="A3" s="296" t="s">
+      <c r="A3" s="282" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="329"/>
-      <c r="C3" s="330"/>
-      <c r="D3" s="330"/>
-      <c r="E3" s="330"/>
-      <c r="F3" s="331"/>
-      <c r="G3" s="279" t="s">
+      <c r="B3" s="390"/>
+      <c r="C3" s="391"/>
+      <c r="D3" s="391"/>
+      <c r="E3" s="391"/>
+      <c r="F3" s="392"/>
+      <c r="G3" s="266" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="278"/>
+      <c r="H3" s="265"/>
       <c r="I3"/>
     </row>
-    <row r="4" spans="1:15" s="226" customFormat="1" ht="16.5">
-      <c r="A4" s="295" t="s">
+    <row r="4" spans="1:15" s="219" customFormat="1" ht="16.5">
+      <c r="A4" s="281" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="329"/>
-      <c r="C4" s="330"/>
-      <c r="D4" s="330"/>
-      <c r="E4" s="330"/>
-      <c r="F4" s="331"/>
-      <c r="G4" s="277" t="s">
-        <v>174</v>
-      </c>
-      <c r="H4" s="276"/>
+      <c r="B4" s="390"/>
+      <c r="C4" s="391"/>
+      <c r="D4" s="391"/>
+      <c r="E4" s="391"/>
+      <c r="F4" s="392"/>
+      <c r="G4" s="264" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="263"/>
       <c r="I4"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
+      <c r="L4" s="216"/>
+      <c r="M4" s="216"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B5" s="332"/>
-      <c r="C5" s="333"/>
-      <c r="D5" s="333"/>
-      <c r="E5" s="333"/>
-      <c r="F5" s="334"/>
-      <c r="G5" s="275" t="s">
-        <v>173</v>
-      </c>
-      <c r="H5" s="274"/>
+      <c r="B5" s="393"/>
+      <c r="C5" s="394"/>
+      <c r="D5" s="394"/>
+      <c r="E5" s="394"/>
+      <c r="F5" s="395"/>
+      <c r="G5" s="262" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="261"/>
       <c r="I5"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B6" s="223"/>
-      <c r="C6" s="223"/>
-      <c r="H6" s="273"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="H6" s="260"/>
       <c r="I6"/>
     </row>
     <row r="7" spans="1:15" ht="16.5">
-      <c r="A7" s="218"/>
-      <c r="B7" s="335" t="s">
+      <c r="A7" s="212"/>
+      <c r="B7" s="396" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="336"/>
-      <c r="D7" s="337"/>
-      <c r="E7" s="225" t="s">
+      <c r="C7" s="397"/>
+      <c r="D7" s="398"/>
+      <c r="E7" s="218" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="225" t="s">
+      <c r="F7" s="218" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="225" t="s">
+      <c r="G7" s="218" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="272">
+      <c r="H7" s="259">
         <f t="shared" ref="H7" si="0">H5</f>
         <v>0</v>
       </c>
-      <c r="I7" s="197" t="s">
-        <v>172</v>
+      <c r="I7" s="192" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="218"/>
-      <c r="B8" s="239" t="s">
+      <c r="A8" s="212"/>
+      <c r="B8" s="232" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="237"/>
-      <c r="D8" s="261"/>
-      <c r="E8" s="262" t="s">
+      <c r="C8" s="230"/>
+      <c r="D8" s="249"/>
+      <c r="E8" s="250" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="202"/>
-      <c r="G8" s="202"/>
-      <c r="H8" s="202"/>
-      <c r="I8" s="203"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="198"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="218"/>
-      <c r="B9" s="206"/>
-      <c r="C9" s="234" t="s">
+      <c r="A9" s="212"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="227" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="221"/>
-      <c r="E9" s="224" t="s">
+      <c r="D9" s="214"/>
+      <c r="E9" s="217" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="248"/>
-      <c r="L9" s="271" t="s">
+      <c r="F9" s="225"/>
+      <c r="G9" s="225"/>
+      <c r="H9" s="225"/>
+      <c r="I9" s="241"/>
+      <c r="L9" s="258" t="s">
         <v>0</v>
       </c>
-      <c r="M9" s="271" t="s">
+      <c r="M9" s="258" t="s">
         <v>1</v>
       </c>
-      <c r="N9" s="271" t="s">
+      <c r="N9" s="258" t="s">
         <v>0</v>
       </c>
-      <c r="O9" s="271" t="s">
+      <c r="O9" s="258" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="218"/>
-      <c r="B10" s="206"/>
-      <c r="C10" s="204"/>
-      <c r="D10" s="268" t="s">
+      <c r="A10" s="212"/>
+      <c r="B10" s="201"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="255" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="270" t="s">
+      <c r="E10" s="257" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="269" t="s">
+      <c r="F10" s="256" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="269" t="s">
+      <c r="G10" s="256" t="s">
         <v>159</v>
       </c>
-      <c r="H10" s="268"/>
-      <c r="I10" s="198"/>
-      <c r="L10" s="241"/>
-      <c r="M10" s="241"/>
-      <c r="N10" s="240"/>
-      <c r="O10" s="240"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="193"/>
+      <c r="L10" s="234"/>
+      <c r="M10" s="234"/>
+      <c r="N10" s="233"/>
+      <c r="O10" s="233"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="218"/>
-      <c r="B11" s="206"/>
-      <c r="C11" s="204"/>
-      <c r="D11" s="247" t="s">
+      <c r="A11" s="212"/>
+      <c r="B11" s="201"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="246"/>
-      <c r="F11" s="245" t="s">
-        <v>179</v>
-      </c>
-      <c r="G11" s="245" t="s">
+      <c r="E11" s="239"/>
+      <c r="F11" s="238" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H11" s="247"/>
-      <c r="I11" s="198"/>
-      <c r="L11" s="241"/>
-      <c r="M11" s="241"/>
-      <c r="N11" s="240"/>
-      <c r="O11" s="240"/>
+      <c r="H11" s="240"/>
+      <c r="I11" s="193"/>
+      <c r="L11" s="234"/>
+      <c r="M11" s="234"/>
+      <c r="N11" s="233"/>
+      <c r="O11" s="233"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="218"/>
-      <c r="B12" s="206"/>
-      <c r="C12" s="204"/>
-      <c r="D12" s="247" t="s">
+      <c r="A12" s="212"/>
+      <c r="B12" s="201"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="240" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="246"/>
-      <c r="F12" s="245" t="s">
+      <c r="E12" s="239"/>
+      <c r="F12" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="245" t="s">
+      <c r="G12" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H12" s="247"/>
-      <c r="I12" s="198"/>
-      <c r="L12" s="241"/>
-      <c r="M12" s="241"/>
-      <c r="N12" s="240"/>
-      <c r="O12" s="240"/>
+      <c r="H12" s="240"/>
+      <c r="I12" s="193"/>
+      <c r="L12" s="234"/>
+      <c r="M12" s="234"/>
+      <c r="N12" s="233"/>
+      <c r="O12" s="233"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="218"/>
-      <c r="B13" s="206"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="247" t="s">
+      <c r="A13" s="212"/>
+      <c r="B13" s="201"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="240" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="246"/>
-      <c r="F13" s="245" t="s">
+      <c r="E13" s="239"/>
+      <c r="F13" s="238" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="245" t="s">
+      <c r="G13" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H13" s="247"/>
-      <c r="I13" s="267"/>
-      <c r="L13" s="241"/>
-      <c r="M13" s="241"/>
-      <c r="N13" s="240"/>
-      <c r="O13" s="240"/>
+      <c r="H13" s="240"/>
+      <c r="I13" s="254"/>
+      <c r="L13" s="234"/>
+      <c r="M13" s="234"/>
+      <c r="N13" s="233"/>
+      <c r="O13" s="233"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="218"/>
-      <c r="B14" s="206"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="247" t="s">
+      <c r="A14" s="212"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="240" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="246"/>
-      <c r="F14" s="245" t="s">
+      <c r="E14" s="239"/>
+      <c r="F14" s="238" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="245" t="s">
+      <c r="G14" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H14" s="247"/>
-      <c r="I14" s="267"/>
-      <c r="L14" s="241"/>
-      <c r="M14" s="241"/>
-      <c r="N14" s="240"/>
-      <c r="O14" s="240"/>
+      <c r="H14" s="240"/>
+      <c r="I14" s="254"/>
+      <c r="L14" s="234"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="233"/>
+      <c r="O14" s="233"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="218"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="247" t="s">
+      <c r="A15" s="212"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="240" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="246"/>
-      <c r="F15" s="245" t="s">
+      <c r="E15" s="239"/>
+      <c r="F15" s="238" t="s">
         <v>111</v>
       </c>
-      <c r="G15" s="245" t="s">
+      <c r="G15" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="247"/>
-      <c r="I15" s="198" t="s">
-        <v>180</v>
-      </c>
-      <c r="L15" s="241"/>
-      <c r="M15" s="241"/>
-      <c r="N15" s="240"/>
-      <c r="O15" s="240"/>
+      <c r="H15" s="240"/>
+      <c r="I15" s="193"/>
+      <c r="L15" s="234"/>
+      <c r="M15" s="234"/>
+      <c r="N15" s="233"/>
+      <c r="O15" s="233"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="218"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="247" t="s">
+      <c r="A16" s="212"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="240" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="246"/>
-      <c r="F16" s="245" t="s">
+      <c r="E16" s="239"/>
+      <c r="F16" s="238" t="s">
         <v>112</v>
       </c>
-      <c r="G16" s="245" t="s">
+      <c r="G16" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H16" s="247"/>
-      <c r="I16" s="198"/>
-      <c r="L16" s="241"/>
-      <c r="M16" s="241"/>
-      <c r="N16" s="240"/>
-      <c r="O16" s="240"/>
+      <c r="H16" s="240"/>
+      <c r="I16" s="193"/>
+      <c r="L16" s="234"/>
+      <c r="M16" s="234"/>
+      <c r="N16" s="233"/>
+      <c r="O16" s="233"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="218"/>
-      <c r="B17" s="206"/>
-      <c r="C17" s="204"/>
-      <c r="D17" s="247" t="s">
+      <c r="A17" s="212"/>
+      <c r="B17" s="201"/>
+      <c r="C17" s="199"/>
+      <c r="D17" s="240" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="246" t="s">
+      <c r="E17" s="239" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="245" t="s">
+      <c r="F17" s="238" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="245" t="s">
+      <c r="G17" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H17" s="247"/>
-      <c r="I17" s="198"/>
-      <c r="L17" s="241"/>
-      <c r="M17" s="241"/>
-      <c r="N17" s="240"/>
-      <c r="O17" s="240"/>
+      <c r="H17" s="240"/>
+      <c r="I17" s="193"/>
+      <c r="L17" s="234"/>
+      <c r="M17" s="234"/>
+      <c r="N17" s="233"/>
+      <c r="O17" s="233"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="218"/>
-      <c r="B18" s="206"/>
-      <c r="C18" s="204"/>
-      <c r="D18" s="247" t="s">
+      <c r="A18" s="212"/>
+      <c r="B18" s="201"/>
+      <c r="C18" s="199"/>
+      <c r="D18" s="240" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="246"/>
-      <c r="F18" s="245" t="s">
+      <c r="E18" s="239"/>
+      <c r="F18" s="238" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="245" t="s">
+      <c r="G18" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H18" s="247"/>
-      <c r="I18" s="198"/>
-      <c r="L18" s="241"/>
-      <c r="M18" s="241"/>
-      <c r="N18" s="240"/>
-      <c r="O18" s="240"/>
+      <c r="H18" s="240"/>
+      <c r="I18" s="193"/>
+      <c r="L18" s="234"/>
+      <c r="M18" s="234"/>
+      <c r="N18" s="233"/>
+      <c r="O18" s="233"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="218"/>
-      <c r="B19" s="206"/>
-      <c r="C19" s="204"/>
-      <c r="D19" s="297" t="s">
+      <c r="A19" s="212"/>
+      <c r="B19" s="201"/>
+      <c r="C19" s="199"/>
+      <c r="D19" s="283" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="298"/>
-      <c r="F19" s="299" t="s">
+      <c r="E19" s="284"/>
+      <c r="F19" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="299" t="s">
+      <c r="G19" s="285" t="s">
         <v>158</v>
       </c>
-      <c r="H19" s="247"/>
-      <c r="I19" s="300" t="s">
-        <v>171</v>
-      </c>
+      <c r="H19" s="240"/>
+      <c r="I19" s="286"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="218"/>
-      <c r="B20" s="206"/>
-      <c r="C20" s="204"/>
-      <c r="D20" s="247" t="s">
+      <c r="A20" s="212"/>
+      <c r="B20" s="201"/>
+      <c r="C20" s="199"/>
+      <c r="D20" s="240" t="s">
         <v>115</v>
       </c>
-      <c r="E20" s="246"/>
-      <c r="F20" s="245" t="s">
+      <c r="E20" s="239"/>
+      <c r="F20" s="238" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="245" t="s">
+      <c r="G20" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="H20" s="247"/>
-      <c r="I20" s="198"/>
-      <c r="L20" s="241"/>
-      <c r="M20" s="241"/>
-      <c r="N20" s="240"/>
-      <c r="O20" s="240"/>
+      <c r="H20" s="240"/>
+      <c r="I20" s="193"/>
+      <c r="L20" s="234"/>
+      <c r="M20" s="234"/>
+      <c r="N20" s="233"/>
+      <c r="O20" s="233"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="218"/>
-      <c r="B21" s="206"/>
-      <c r="C21" s="234" t="s">
+      <c r="A21" s="212"/>
+      <c r="B21" s="213"/>
+      <c r="C21" s="227" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="264"/>
-      <c r="E21" s="266" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="265"/>
-      <c r="G21" s="265"/>
-      <c r="H21" s="264"/>
-      <c r="I21" s="248"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="225" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="241"/>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="218"/>
-      <c r="B22" s="206"/>
-      <c r="C22" s="207"/>
-      <c r="D22" s="263"/>
-      <c r="E22" s="282"/>
-      <c r="F22" s="254"/>
-      <c r="G22" s="211"/>
-      <c r="H22" s="219" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="259"/>
-      <c r="L22" s="241"/>
-      <c r="M22" s="241"/>
-      <c r="N22" s="240"/>
-      <c r="O22" s="240"/>
+    <row r="22" spans="1:15" ht="30">
+      <c r="A22" s="212"/>
+      <c r="B22" s="213"/>
+      <c r="C22" s="200"/>
+      <c r="D22" s="216" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" s="205" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="245" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="205" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="204" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="269"/>
+      <c r="L22" s="234"/>
+      <c r="M22" s="234"/>
+      <c r="N22" s="233"/>
+      <c r="O22" s="233"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="218"/>
-      <c r="B23" s="220"/>
-      <c r="C23" s="234" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="233"/>
-      <c r="E23" s="232" t="s">
-        <v>182</v>
-      </c>
-      <c r="F23" s="232"/>
-      <c r="G23" s="232"/>
-      <c r="H23" s="232"/>
+      <c r="A23" s="212"/>
+      <c r="B23" s="232" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="270"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="250" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="249"/>
+      <c r="G23" s="249"/>
+      <c r="H23" s="249"/>
       <c r="I23" s="248"/>
     </row>
-    <row r="24" spans="1:15" ht="30">
-      <c r="A24" s="218"/>
-      <c r="B24" s="220"/>
-      <c r="C24" s="205"/>
-      <c r="D24" s="223" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24" s="211" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="254" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="211" t="s">
-        <v>157</v>
-      </c>
-      <c r="H24" s="210" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="283"/>
-      <c r="L24" s="241"/>
-      <c r="M24" s="241"/>
-      <c r="N24" s="240"/>
-      <c r="O24" s="240"/>
+    <row r="24" spans="1:15">
+      <c r="A24" s="212"/>
+      <c r="B24" s="201"/>
+      <c r="C24" s="227" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="214"/>
+      <c r="E24" s="217" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="225"/>
+      <c r="G24" s="225"/>
+      <c r="H24" s="225"/>
+      <c r="I24" s="195"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="218"/>
-      <c r="B25" s="239" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="284"/>
-      <c r="D25" s="261"/>
-      <c r="E25" s="262" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="261"/>
-      <c r="G25" s="261"/>
-      <c r="H25" s="261"/>
-      <c r="I25" s="260"/>
+      <c r="A25" s="212"/>
+      <c r="B25" s="201"/>
+      <c r="C25" s="199"/>
+      <c r="D25" s="240" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="239" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="238" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="240" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="247"/>
+      <c r="L25" s="234"/>
+      <c r="M25" s="234"/>
+      <c r="N25" s="233"/>
+      <c r="O25" s="233"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="218"/>
-      <c r="B26" s="206"/>
-      <c r="C26" s="234" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="221"/>
-      <c r="E26" s="224" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="232"/>
-      <c r="G26" s="232"/>
-      <c r="H26" s="232"/>
-      <c r="I26" s="200"/>
+      <c r="A26" s="212"/>
+      <c r="B26" s="201"/>
+      <c r="C26" s="199"/>
+      <c r="D26" s="240" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="239" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="238" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="238" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="243" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" s="203"/>
+      <c r="L26" s="234"/>
+      <c r="M26" s="234"/>
+      <c r="N26" s="233"/>
+      <c r="O26" s="233"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="218"/>
-      <c r="B27" s="206"/>
-      <c r="C27" s="204"/>
-      <c r="D27" s="247" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="246" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="245" t="s">
-        <v>112</v>
-      </c>
-      <c r="G27" s="245" t="s">
-        <v>145</v>
-      </c>
-      <c r="H27" s="247" t="s">
-        <v>107</v>
-      </c>
-      <c r="I27" s="259"/>
-      <c r="L27" s="241"/>
-      <c r="M27" s="241"/>
-      <c r="N27" s="240"/>
-      <c r="O27" s="240"/>
+      <c r="A27" s="212"/>
+      <c r="B27" s="201"/>
+      <c r="C27" s="199"/>
+      <c r="D27" s="240" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="239"/>
+      <c r="F27" s="238" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="238" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="243" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="246"/>
+      <c r="L27" s="234"/>
+      <c r="M27" s="234"/>
+      <c r="N27" s="233"/>
+      <c r="O27" s="233"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="218"/>
-      <c r="B28" s="206"/>
-      <c r="C28" s="204"/>
-      <c r="D28" s="247" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="246" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="245" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28" s="245" t="s">
+      <c r="A28" s="212"/>
+      <c r="B28" s="201"/>
+      <c r="C28" s="199"/>
+      <c r="D28" s="283" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="284"/>
+      <c r="F28" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="H28" s="251" t="s">
+      <c r="H28" s="283" t="s">
         <v>117</v>
       </c>
-      <c r="I28" s="208"/>
-      <c r="L28" s="241"/>
-      <c r="M28" s="241"/>
-      <c r="N28" s="240"/>
-      <c r="O28" s="240"/>
+      <c r="I28" s="361"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="218"/>
-      <c r="B29" s="206"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="247" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="246"/>
-      <c r="F29" s="245" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" s="245" t="s">
+      <c r="A29" s="212"/>
+      <c r="B29" s="201"/>
+      <c r="C29" s="199"/>
+      <c r="D29" s="240" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="239"/>
+      <c r="F29" s="238" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="238" t="s">
         <v>144</v>
       </c>
-      <c r="H29" s="251" t="s">
+      <c r="H29" s="243" t="s">
         <v>117</v>
       </c>
-      <c r="I29" s="258"/>
-      <c r="L29" s="241"/>
-      <c r="M29" s="241"/>
-      <c r="N29" s="240"/>
-      <c r="O29" s="240"/>
+      <c r="I29" s="193"/>
+      <c r="L29" s="234"/>
+      <c r="M29" s="234"/>
+      <c r="N29" s="233"/>
+      <c r="O29" s="233"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="218"/>
-      <c r="B30" s="206"/>
-      <c r="C30" s="204"/>
-      <c r="D30" s="251" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="257"/>
-      <c r="F30" s="256" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="256" t="s">
-        <v>144</v>
-      </c>
-      <c r="H30" s="251" t="s">
+      <c r="A30" s="212"/>
+      <c r="B30" s="201"/>
+      <c r="C30" s="199"/>
+      <c r="D30" s="204" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="205"/>
+      <c r="F30" s="245" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="245" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" s="243" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="255" t="s">
-        <v>171</v>
-      </c>
+      <c r="I30" s="244"/>
+      <c r="L30" s="234"/>
+      <c r="M30" s="234"/>
+      <c r="N30" s="233"/>
+      <c r="O30" s="233"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="218"/>
-      <c r="B31" s="206"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="247" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="246"/>
-      <c r="F31" s="245" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" s="245" t="s">
-        <v>144</v>
-      </c>
-      <c r="H31" s="251" t="s">
+      <c r="A31" s="212"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="199"/>
+      <c r="D31" s="358" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359" t="s">
+        <v>160</v>
+      </c>
+      <c r="G31" s="359" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="358" t="s">
         <v>117</v>
       </c>
-      <c r="I31" s="198"/>
-      <c r="L31" s="241"/>
-      <c r="M31" s="241"/>
-      <c r="N31" s="240"/>
-      <c r="O31" s="240"/>
+      <c r="I31" s="360"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="218"/>
-      <c r="B32" s="206"/>
-      <c r="C32" s="204"/>
-      <c r="D32" s="210" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="211"/>
-      <c r="F32" s="254" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="254" t="s">
-        <v>169</v>
-      </c>
-      <c r="H32" s="251" t="s">
-        <v>117</v>
-      </c>
-      <c r="I32" s="253"/>
-      <c r="L32" s="241"/>
-      <c r="M32" s="241"/>
-      <c r="N32" s="240"/>
-      <c r="O32" s="240"/>
+      <c r="A32" s="212"/>
+      <c r="B32" s="201"/>
+      <c r="C32" s="227" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="226"/>
+      <c r="E32" s="225" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" s="242"/>
+      <c r="G32" s="242"/>
+      <c r="H32" s="226"/>
+      <c r="I32" s="241"/>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="218"/>
-      <c r="B33" s="206"/>
-      <c r="C33" s="204"/>
-      <c r="D33" s="209" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="252" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="209" t="s">
+      <c r="A33" s="212"/>
+      <c r="B33" s="201"/>
+      <c r="C33" s="200"/>
+      <c r="D33" s="240" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" s="239" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="238" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" s="237" t="s">
+        <v>164</v>
+      </c>
+      <c r="H33" s="236" t="s">
         <v>117</v>
       </c>
-      <c r="I33" s="250" t="s">
-        <v>168</v>
-      </c>
+      <c r="I33" s="235"/>
+      <c r="L33" s="234"/>
+      <c r="M33" s="234"/>
+      <c r="N33" s="233"/>
+      <c r="O33" s="233"/>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="218"/>
-      <c r="B34" s="206"/>
-      <c r="C34" s="234" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="233"/>
-      <c r="E34" s="232" t="s">
-        <v>167</v>
-      </c>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="233"/>
-      <c r="I34" s="248"/>
+      <c r="A34" s="212"/>
+      <c r="B34" s="201"/>
+      <c r="C34" s="288" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="289"/>
+      <c r="E34" s="289" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="289"/>
+      <c r="G34" s="289"/>
+      <c r="H34" s="289"/>
+      <c r="I34" s="290"/>
+      <c r="L34" s="282"/>
+      <c r="M34" s="282"/>
+      <c r="N34" s="287"/>
+      <c r="O34" s="287"/>
     </row>
-    <row r="35" spans="1:15" ht="30">
-      <c r="A35" s="218"/>
-      <c r="B35" s="206"/>
-      <c r="C35" s="205"/>
-      <c r="D35" s="247" t="s">
+    <row r="35" spans="1:15">
+      <c r="A35" s="212"/>
+      <c r="B35" s="201"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="291" t="s">
         <v>89</v>
       </c>
-      <c r="E35" s="246" t="s">
-        <v>166</v>
-      </c>
-      <c r="F35" s="245" t="s">
-        <v>165</v>
-      </c>
-      <c r="G35" s="244" t="s">
-        <v>164</v>
-      </c>
-      <c r="H35" s="243" t="s">
+      <c r="E35" s="292" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" s="240" t="s">
         <v>117</v>
       </c>
-      <c r="I35" s="242"/>
-      <c r="L35" s="241"/>
-      <c r="M35" s="241"/>
-      <c r="N35" s="240"/>
-      <c r="O35" s="240"/>
+      <c r="I35" s="293"/>
+      <c r="L35" s="234"/>
+      <c r="M35" s="234"/>
+      <c r="N35" s="233"/>
+      <c r="O35" s="233"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="218"/>
-      <c r="B36" s="206"/>
-      <c r="C36" s="339" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340" t="s">
+      <c r="A36" s="212"/>
+      <c r="B36" s="201"/>
+      <c r="C36" s="199"/>
+      <c r="D36" s="204" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="205"/>
+      <c r="F36" s="294" t="s">
         <v>183</v>
       </c>
-      <c r="F36" s="340"/>
-      <c r="G36" s="340"/>
-      <c r="H36" s="340"/>
-      <c r="I36" s="341"/>
-      <c r="L36" s="296"/>
-      <c r="M36" s="296"/>
-      <c r="N36" s="338"/>
-      <c r="O36" s="338"/>
+      <c r="G36" s="294" t="s">
+        <v>184</v>
+      </c>
+      <c r="H36" s="243" t="s">
+        <v>117</v>
+      </c>
+      <c r="I36" s="295"/>
+      <c r="L36" s="234"/>
+      <c r="M36" s="234"/>
+      <c r="N36" s="233"/>
+      <c r="O36" s="233"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="218"/>
-      <c r="B37" s="206"/>
-      <c r="C37" s="204"/>
-      <c r="D37" s="342" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="343" t="s">
-        <v>191</v>
-      </c>
-      <c r="F37" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="G37" s="46" t="s">
+      <c r="A37" s="212"/>
+      <c r="B37" s="201"/>
+      <c r="C37" s="200"/>
+      <c r="D37" s="296" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="297"/>
+      <c r="F37" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="H37" s="243" t="s">
+      <c r="G37" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="H37" s="283" t="s">
         <v>117</v>
       </c>
-      <c r="I37" s="344"/>
-      <c r="L37" s="241"/>
-      <c r="M37" s="241"/>
-      <c r="N37" s="240"/>
-      <c r="O37" s="240"/>
+      <c r="I37" s="298"/>
+      <c r="L37" s="234"/>
+      <c r="M37" s="234"/>
+      <c r="N37" s="233"/>
+      <c r="O37" s="233"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="218"/>
-      <c r="B38" s="206"/>
-      <c r="C38" s="204"/>
-      <c r="D38" s="210" t="s">
-        <v>186</v>
-      </c>
-      <c r="E38" s="211"/>
-      <c r="F38" s="345" t="s">
-        <v>187</v>
-      </c>
-      <c r="G38" s="345" t="s">
-        <v>188</v>
-      </c>
-      <c r="H38" s="243" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="346"/>
-      <c r="L38" s="241"/>
-      <c r="M38" s="241"/>
-      <c r="N38" s="240"/>
-      <c r="O38" s="240"/>
+      <c r="A38" s="212"/>
+      <c r="B38" s="201"/>
+      <c r="C38" s="227" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="251"/>
+      <c r="E38" s="253" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="252"/>
+      <c r="G38" s="252"/>
+      <c r="H38" s="251"/>
+      <c r="I38" s="241"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="218"/>
-      <c r="B39" s="206"/>
-      <c r="C39" s="205"/>
-      <c r="D39" s="347" t="s">
-        <v>91</v>
-      </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H39" s="243" t="s">
+      <c r="A39" s="212"/>
+      <c r="B39" s="201"/>
+      <c r="C39" s="202"/>
+      <c r="D39" s="400"/>
+      <c r="E39" s="401"/>
+      <c r="F39" s="402"/>
+      <c r="G39" s="403"/>
+      <c r="H39" s="399" t="s">
         <v>117</v>
       </c>
-      <c r="I39" s="349"/>
-      <c r="L39" s="241"/>
-      <c r="M39" s="241"/>
-      <c r="N39" s="240"/>
-      <c r="O39" s="240"/>
+      <c r="I39" s="247"/>
+      <c r="L39" s="234"/>
+      <c r="M39" s="234"/>
+      <c r="N39" s="233"/>
+      <c r="O39" s="233"/>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="218"/>
-      <c r="B40" s="239" t="s">
+      <c r="A40" s="212"/>
+      <c r="B40" s="232" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="237"/>
-      <c r="D40" s="238"/>
-      <c r="E40" s="237" t="s">
+      <c r="C40" s="230"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="230" t="s">
         <v>120</v>
       </c>
-      <c r="F40" s="237"/>
-      <c r="G40" s="237"/>
-      <c r="H40" s="236"/>
-      <c r="I40" s="235"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="228"/>
     </row>
     <row r="41" spans="1:15">
-      <c r="B41" s="206"/>
-      <c r="C41" s="234" t="s">
+      <c r="B41" s="201"/>
+      <c r="C41" s="227" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="233"/>
-      <c r="E41" s="232" t="s">
+      <c r="D41" s="226"/>
+      <c r="E41" s="225" t="s">
         <v>29</v>
       </c>
-      <c r="F41" s="232"/>
-      <c r="G41" s="232"/>
-      <c r="H41" s="224"/>
-      <c r="I41" s="231"/>
+      <c r="F41" s="225"/>
+      <c r="G41" s="225"/>
+      <c r="H41" s="217"/>
+      <c r="I41" s="224"/>
     </row>
     <row r="42" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B42" s="201"/>
-      <c r="C42" s="199"/>
-      <c r="D42" s="212" t="s">
+      <c r="B42" s="196"/>
+      <c r="C42" s="194"/>
+      <c r="D42" s="206" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="213"/>
-      <c r="F42" s="214" t="s">
+      <c r="E42" s="207"/>
+      <c r="F42" s="208" t="s">
         <v>143</v>
       </c>
-      <c r="G42" s="215" t="s">
+      <c r="G42" s="209" t="s">
         <v>121</v>
       </c>
-      <c r="H42" s="216" t="s">
+      <c r="H42" s="210" t="s">
         <v>114</v>
       </c>
-      <c r="I42" s="230"/>
-      <c r="L42" s="241"/>
-      <c r="M42" s="229"/>
-      <c r="N42" s="228"/>
-      <c r="O42" s="228"/>
+      <c r="I42" s="223"/>
+      <c r="L42" s="234"/>
+      <c r="M42" s="222"/>
+      <c r="N42" s="221"/>
+      <c r="O42" s="221"/>
     </row>
     <row r="44" spans="1:15">
       <c r="F44"/>
       <c r="G44"/>
-      <c r="I44" s="223"/>
+      <c r="I44" s="216"/>
     </row>
     <row r="45" spans="1:15">
       <c r="F45"/>
       <c r="G45"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="E46" s="296"/>
+      <c r="E46" s="282"/>
       <c r="F46"/>
       <c r="G46"/>
       <c r="I46"/>
     </row>
     <row r="47" spans="1:15">
       <c r="F47"/>
-      <c r="G47" s="292"/>
+      <c r="G47" s="278"/>
       <c r="I47"/>
     </row>
     <row r="48" spans="1:15">
       <c r="F48"/>
-      <c r="G48" s="292"/>
+      <c r="G48" s="278"/>
       <c r="I48"/>
     </row>
     <row r="49" spans="6:13">
@@ -28100,149 +28074,149 @@
     </row>
     <row r="52" spans="6:13">
       <c r="F52"/>
-      <c r="G52" s="281"/>
-      <c r="H52" s="175"/>
+      <c r="G52" s="268"/>
+      <c r="H52" s="171"/>
       <c r="I52"/>
     </row>
     <row r="53" spans="6:13" ht="16.5">
       <c r="F53"/>
-      <c r="G53" s="281"/>
-      <c r="H53" s="293"/>
+      <c r="G53" s="268"/>
+      <c r="H53" s="279"/>
       <c r="I53"/>
     </row>
-    <row r="54" spans="6:13" s="226" customFormat="1">
-      <c r="G54" s="281"/>
-      <c r="H54" s="227"/>
-      <c r="L54" s="223"/>
-      <c r="M54" s="223"/>
+    <row r="54" spans="6:13" s="219" customFormat="1">
+      <c r="G54" s="268"/>
+      <c r="H54" s="220"/>
+      <c r="L54" s="216"/>
+      <c r="M54" s="216"/>
     </row>
-    <row r="55" spans="6:13" s="226" customFormat="1">
-      <c r="G55" s="281"/>
-      <c r="H55" s="227"/>
-      <c r="L55" s="223"/>
-      <c r="M55" s="223"/>
+    <row r="55" spans="6:13" s="219" customFormat="1">
+      <c r="G55" s="268"/>
+      <c r="H55" s="220"/>
+      <c r="L55" s="216"/>
+      <c r="M55" s="216"/>
     </row>
-    <row r="56" spans="6:13" s="226" customFormat="1">
-      <c r="G56" s="281"/>
-      <c r="H56" s="227"/>
-      <c r="L56" s="223"/>
-      <c r="M56" s="223"/>
+    <row r="56" spans="6:13" s="219" customFormat="1">
+      <c r="G56" s="268"/>
+      <c r="H56" s="220"/>
+      <c r="L56" s="216"/>
+      <c r="M56" s="216"/>
     </row>
-    <row r="57" spans="6:13" s="226" customFormat="1">
-      <c r="G57" s="281"/>
-      <c r="H57" s="227"/>
-      <c r="L57" s="223"/>
-      <c r="M57" s="223"/>
+    <row r="57" spans="6:13" s="219" customFormat="1">
+      <c r="G57" s="268"/>
+      <c r="H57" s="220"/>
+      <c r="L57" s="216"/>
+      <c r="M57" s="216"/>
     </row>
-    <row r="58" spans="6:13" s="226" customFormat="1">
-      <c r="G58" s="281"/>
-      <c r="H58" s="227"/>
-      <c r="L58" s="223"/>
-      <c r="M58" s="223"/>
+    <row r="58" spans="6:13" s="219" customFormat="1">
+      <c r="G58" s="268"/>
+      <c r="H58" s="220"/>
+      <c r="L58" s="216"/>
+      <c r="M58" s="216"/>
     </row>
-    <row r="59" spans="6:13" s="226" customFormat="1">
-      <c r="G59" s="281"/>
-      <c r="H59" s="227"/>
-      <c r="L59" s="223"/>
-      <c r="M59" s="223"/>
+    <row r="59" spans="6:13" s="219" customFormat="1">
+      <c r="G59" s="268"/>
+      <c r="H59" s="220"/>
+      <c r="L59" s="216"/>
+      <c r="M59" s="216"/>
     </row>
-    <row r="60" spans="6:13" s="226" customFormat="1">
-      <c r="G60" s="281"/>
-      <c r="H60" s="227"/>
-      <c r="L60" s="223"/>
-      <c r="M60" s="223"/>
+    <row r="60" spans="6:13" s="219" customFormat="1">
+      <c r="G60" s="268"/>
+      <c r="H60" s="220"/>
+      <c r="L60" s="216"/>
+      <c r="M60" s="216"/>
     </row>
-    <row r="61" spans="6:13" s="226" customFormat="1">
-      <c r="G61" s="281"/>
-      <c r="H61" s="222"/>
-      <c r="L61" s="223"/>
-      <c r="M61" s="223"/>
+    <row r="61" spans="6:13" s="219" customFormat="1">
+      <c r="G61" s="268"/>
+      <c r="H61" s="215"/>
+      <c r="L61" s="216"/>
+      <c r="M61" s="216"/>
     </row>
-    <row r="62" spans="6:13" s="226" customFormat="1">
-      <c r="G62" s="281"/>
-      <c r="H62" s="222"/>
-      <c r="L62" s="223"/>
-      <c r="M62" s="223"/>
+    <row r="62" spans="6:13" s="219" customFormat="1">
+      <c r="G62" s="268"/>
+      <c r="H62" s="215"/>
+      <c r="L62" s="216"/>
+      <c r="M62" s="216"/>
     </row>
-    <row r="63" spans="6:13" s="226" customFormat="1">
-      <c r="H63" s="222"/>
-      <c r="L63" s="223"/>
-      <c r="M63" s="223"/>
+    <row r="63" spans="6:13" s="219" customFormat="1">
+      <c r="H63" s="215"/>
+      <c r="L63" s="216"/>
+      <c r="M63" s="216"/>
     </row>
-    <row r="64" spans="6:13" s="226" customFormat="1">
-      <c r="H64" s="222"/>
-      <c r="L64" s="223"/>
-      <c r="M64" s="223"/>
+    <row r="64" spans="6:13" s="219" customFormat="1">
+      <c r="H64" s="215"/>
+      <c r="L64" s="216"/>
+      <c r="M64" s="216"/>
     </row>
     <row r="65" spans="6:15">
-      <c r="H65" s="175"/>
+      <c r="H65" s="171"/>
     </row>
     <row r="66" spans="6:15">
-      <c r="H66" s="175"/>
+      <c r="H66" s="171"/>
     </row>
     <row r="67" spans="6:15">
-      <c r="H67" s="175"/>
+      <c r="H67" s="171"/>
     </row>
     <row r="68" spans="6:15">
-      <c r="H68" s="175"/>
+      <c r="H68" s="171"/>
     </row>
     <row r="69" spans="6:15">
-      <c r="H69" s="175"/>
+      <c r="H69" s="171"/>
     </row>
     <row r="70" spans="6:15">
-      <c r="H70" s="175"/>
+      <c r="H70" s="171"/>
     </row>
     <row r="71" spans="6:15">
       <c r="F71"/>
       <c r="G71"/>
-      <c r="H71" s="175"/>
+      <c r="H71" s="171"/>
     </row>
     <row r="72" spans="6:15">
       <c r="F72"/>
       <c r="G72"/>
-      <c r="H72" s="175"/>
+      <c r="H72" s="171"/>
     </row>
     <row r="73" spans="6:15">
       <c r="F73"/>
       <c r="G73"/>
-      <c r="H73" s="175"/>
+      <c r="H73" s="171"/>
     </row>
     <row r="74" spans="6:15">
       <c r="F74"/>
       <c r="G74"/>
-      <c r="H74" s="175"/>
+      <c r="H74" s="171"/>
     </row>
     <row r="75" spans="6:15">
       <c r="F75"/>
       <c r="G75"/>
-      <c r="H75" s="175"/>
-      <c r="I75" s="175"/>
-      <c r="J75" s="175"/>
-      <c r="K75" s="175"/>
+      <c r="H75" s="171"/>
+      <c r="I75" s="171"/>
+      <c r="J75" s="171"/>
+      <c r="K75" s="171"/>
       <c r="L75" s="8"/>
       <c r="M75" s="8"/>
-      <c r="N75" s="175"/>
-      <c r="O75" s="175"/>
+      <c r="N75" s="171"/>
+      <c r="O75" s="171"/>
     </row>
     <row r="76" spans="6:15">
       <c r="F76"/>
       <c r="G76"/>
-      <c r="H76" s="175"/>
+      <c r="H76" s="171"/>
     </row>
     <row r="77" spans="6:15">
       <c r="F77"/>
       <c r="G77"/>
-      <c r="H77" s="175"/>
+      <c r="H77" s="171"/>
     </row>
     <row r="78" spans="6:15">
       <c r="F78"/>
       <c r="G78"/>
-      <c r="H78" s="175"/>
+      <c r="H78" s="171"/>
     </row>
     <row r="79" spans="6:15">
       <c r="F79"/>
       <c r="G79"/>
-      <c r="H79" s="175"/>
+      <c r="H79" s="171"/>
     </row>
     <row r="80" spans="6:15">
       <c r="F80"/>
@@ -28257,10 +28231,10 @@
       <c r="G82"/>
     </row>
     <row r="86" spans="6:8">
-      <c r="H86" s="175"/>
+      <c r="H86" s="171"/>
     </row>
     <row r="87" spans="6:8">
-      <c r="H87" s="175"/>
+      <c r="H87" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="2">
